--- a/GearSage-client/pkgGear/data_raw/shimano_spinning_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_spinning_reels_import.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Reels Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Reels Variants" sheetId="2" r:id="rId2"/>
+    <sheet name="reel" sheetId="1" r:id="rId1"/>
+    <sheet name="spinning_reel_detail" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -452,7 +452,7 @@
         <v>SRE1000</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="str">
         <v>STELLA SW</v>
@@ -476,10 +476,10 @@
         <v>images/shimano_reels/STELLA SW_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -499,7 +499,7 @@
         <v>SRE1001</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="str">
         <v>BB-X TECHNIUM FIRE BLOOD</v>
@@ -523,10 +523,10 @@
         <v>images/shimano_reels/BB-X TECHNIUM FIRE BLOOD_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v>SRE1002</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v>BB-X TECHNIUM</v>
@@ -570,10 +570,10 @@
         <v>images/shimano_reels/BB-X TECHNIUM_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -593,7 +593,7 @@
         <v>SRE1003</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="str">
         <v>KISU SPECIAL 45</v>
@@ -617,10 +617,10 @@
         <v>images/shimano_reels/KISU SPECIAL 45_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -640,7 +640,7 @@
         <v>SRE1004</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="str">
         <v>AERO TECHNIUM MGS XTD</v>
@@ -664,10 +664,10 @@
         <v>images/shimano_reels/AERO TECHNIUM MGS XTD_main.jpg</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -687,7 +687,7 @@
         <v>SRE1005</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v>AERO TECHNIUM MGS XSD</v>
@@ -711,10 +711,10 @@
         <v>images/shimano_reels/AERO TECHNIUM MGS XSD_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -734,7 +734,7 @@
         <v>SRE1006</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="str">
         <v>STELLA</v>
@@ -758,10 +758,10 @@
         <v>images/shimano_reels/STELLA_main.jpg</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>SRE1007</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="str">
         <v>EXSENCE</v>
@@ -805,10 +805,10 @@
         <v>images/shimano_reels/EXSENCE_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -828,7 +828,7 @@
         <v>SRE1008</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="str">
         <v>TWINPOWER SW</v>
@@ -852,10 +852,10 @@
         <v>images/shimano_reels/TWINPOWER SW_main.jpg</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -875,7 +875,7 @@
         <v>SRE1009</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="str">
         <v>POWER AERO XTC</v>
@@ -899,10 +899,10 @@
         <v>images/shimano_reels/POWER AERO XTC_main.jpg</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -922,7 +922,7 @@
         <v>SRE1010</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="str">
         <v>POWER AERO XSC</v>
@@ -946,10 +946,10 @@
         <v>images/shimano_reels/POWER AERO XSC_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -969,7 +969,7 @@
         <v>SRE1011</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="str">
         <v>BB-X HYPER FORCE TYPE2</v>
@@ -993,10 +993,10 @@
         <v>images/shimano_reels/BB-X HYPER FORCE TYPE2_main.jpg</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1016,7 +1016,7 @@
         <v>SRE1012</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="str">
         <v>FLIEGEN</v>
@@ -1040,10 +1040,10 @@
         <v>images/shimano_reels/FLIEGEN_main.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1063,7 +1063,7 @@
         <v>SRE1013</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="str">
         <v>Vanquish CE</v>
@@ -1087,10 +1087,10 @@
         <v>images/shimano_reels/Vanquish CE_main.jpg</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1110,7 +1110,7 @@
         <v>SRE1014</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="str">
         <v>Vanquish</v>
@@ -1134,10 +1134,10 @@
         <v>images/shimano_reels/Vanquish_main.jpg</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1157,7 +1157,7 @@
         <v>SRE1015</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="str">
         <v>SARAGOSA SW</v>
@@ -1181,10 +1181,10 @@
         <v>images/shimano_reels/SARAGOSA SW_main.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1204,7 +1204,7 @@
         <v>SRE1016</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="str">
         <v>BB-X HYPER FORCE</v>
@@ -1228,10 +1228,10 @@
         <v>images/shimano_reels/BB-X HYPER FORCE_main.jpg</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1251,7 +1251,7 @@
         <v>SRE1017</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="str">
         <v>BB-X Remare</v>
@@ -1275,10 +1275,10 @@
         <v>images/shimano_reels/BB-X Remare_main.jpg</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1298,7 +1298,7 @@
         <v>SRE1018</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="str">
         <v>TWINPOWER</v>
@@ -1322,10 +1322,10 @@
         <v>images/shimano_reels/TWINPOWER_main.jpg</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1345,7 +1345,7 @@
         <v>SRE1019</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="str">
         <v>TWINPOWER XD</v>
@@ -1369,10 +1369,10 @@
         <v>images/shimano_reels/TWINPOWER XD_main.jpg</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1392,7 +1392,7 @@
         <v>SRE1020</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="str">
         <v>HYPER FORCE LB</v>
@@ -1416,10 +1416,10 @@
         <v>images/shimano_reels/HYPER FORCE LB_main.jpg</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1439,7 +1439,7 @@
         <v>SRE1021</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="str">
         <v>POWER AERO TD</v>
@@ -1463,10 +1463,10 @@
         <v>images/shimano_reels/POWER AERO TD_main.jpg</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1486,7 +1486,7 @@
         <v>SRE1022</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="str">
         <v>ULTEGRA XR BIG PIT XTD</v>
@@ -1510,10 +1510,10 @@
         <v>images/shimano_reels/ULTEGRA XR BIG PIT XTD_main.jpg</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1533,7 +1533,7 @@
         <v>SRE1023</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="str">
         <v>ULTEGRA XR BIG PIT XSD</v>
@@ -1557,10 +1557,10 @@
         <v>images/shimano_reels/ULTEGRA XR BIG PIT XSD_main.jpg</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1580,7 +1580,7 @@
         <v>SRE1024</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="str">
         <v>BB-X HYPER FORCE 1700/C2000</v>
@@ -1604,10 +1604,10 @@
         <v>images/shimano_reels/BB-X HYPER FORCE 1700_C2000_main.jpg</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1627,7 +1627,7 @@
         <v>SRE1025</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="str">
         <v>BB-X Rinkai SP</v>
@@ -1651,10 +1651,10 @@
         <v>images/shimano_reels/BB-X Rinkai SP_main.jpg</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1674,7 +1674,7 @@
         <v>SRE1026</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="str">
         <v>EXSENCE XR</v>
@@ -1698,10 +1698,10 @@
         <v>images/shimano_reels/EXSENCE XR_main.jpg</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1721,7 +1721,7 @@
         <v>SRE1027</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="str">
         <v>STRADIC SW</v>
@@ -1745,10 +1745,10 @@
         <v>images/shimano_reels/STRADIC SW_main.jpg</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1768,7 +1768,7 @@
         <v>SRE1028</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="str">
         <v>Sephia XR</v>
@@ -1792,10 +1792,10 @@
         <v>images/shimano_reels/Sephia XR_main.jpg</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1815,7 +1815,7 @@
         <v>SRE1029</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="str">
         <v>SUSTAIN</v>
@@ -1839,10 +1839,10 @@
         <v>images/shimano_reels/SUSTAIN_main.jpg</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -1862,7 +1862,7 @@
         <v>SRE1030</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="str">
         <v>Soare XR</v>
@@ -1886,10 +1886,10 @@
         <v>images/shimano_reels/Soare XR_main.jpg</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1909,7 +1909,7 @@
         <v>SRE1031</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="str">
         <v>CARDIFF XR</v>
@@ -1933,10 +1933,10 @@
         <v>images/shimano_reels/CARDIFF XR_main.jpg</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1956,7 +1956,7 @@
         <v>SRE1032</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="str">
         <v>BB-X DESPINA</v>
@@ -1980,10 +1980,10 @@
         <v>images/shimano_reels/BB-X DESPINA_main.jpg</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>SRE1033</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="str">
         <v>BULL‘S EYE</v>
@@ -2027,10 +2027,10 @@
         <v>images/shimano_reels/BULL‘S EYE_main.jpg</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -2050,7 +2050,7 @@
         <v>SRE1034</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="str">
         <v>COMPLEX XR</v>
@@ -2074,10 +2074,10 @@
         <v>images/shimano_reels/COMPLEX XR_main.jpg</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -2097,7 +2097,7 @@
         <v>SRE1035</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="str">
         <v>BAITRUNNER CI4+ XTB</v>
@@ -2121,10 +2121,10 @@
         <v>images/shimano_reels/BAITRUNNER CI4+ XTB_main.jpg</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -2144,7 +2144,7 @@
         <v>SRE1036</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="str">
         <v>SURF LEADER</v>
@@ -2168,10 +2168,10 @@
         <v>images/shimano_reels/SURF LEADER_main.png</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -2191,7 +2191,7 @@
         <v>SRE1037</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="str">
         <v>Sephia SS</v>
@@ -2215,10 +2215,10 @@
         <v>images/shimano_reels/Sephia SS_main.jpg</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2238,7 +2238,7 @@
         <v>SRE1038</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="str">
         <v>VANFORD</v>
@@ -2262,10 +2262,10 @@
         <v>images/shimano_reels/VANFORD_main.jpg</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2285,7 +2285,7 @@
         <v>SRE1039</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="str">
         <v>ULTEGRA XS</v>
@@ -2309,10 +2309,10 @@
         <v>images/shimano_reels/ULTEGRA XS_main.jpg</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2332,7 +2332,7 @@
         <v>SRE1040</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="str">
         <v>ULTEGRA XT</v>
@@ -2356,10 +2356,10 @@
         <v>images/shimano_reels/ULTEGRA XT_main.jpg</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2379,7 +2379,7 @@
         <v>SRE1041</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="str">
         <v>BB-X LARISSA</v>
@@ -2403,10 +2403,10 @@
         <v>images/shimano_reels/BB-X LARISSA_main.jpg</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2426,7 +2426,7 @@
         <v>SRE1042</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="str">
         <v>SPHEROS SW</v>
@@ -2450,10 +2450,10 @@
         <v>images/shimano_reels/SPHEROS SW_main.jpg</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2473,7 +2473,7 @@
         <v>SRE1043</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="str">
         <v>SPEEDMASTER XTD</v>
@@ -2497,10 +2497,10 @@
         <v>images/shimano_reels/SPEEDMASTER XTD_main.jpg</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2520,7 +2520,7 @@
         <v>SRE1044</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="str">
         <v>STRADIC</v>
@@ -2544,10 +2544,10 @@
         <v>images/shimano_reels/STRADIC_main.jpg</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>SRE1045</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="str">
         <v>SUPER AERO SpinJoy</v>
@@ -2591,10 +2591,10 @@
         <v>images/shimano_reels/SUPER AERO SpinJoy_main.jpg</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2614,7 +2614,7 @@
         <v>SRE1046</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" t="str">
         <v>SPEEDMASTER XSD</v>
@@ -2638,10 +2638,10 @@
         <v>images/shimano_reels/SPEEDMASTER XSD_main.jpg</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2661,7 +2661,7 @@
         <v>SRE1047</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="str">
         <v>Sephia BB</v>
@@ -2685,10 +2685,10 @@
         <v>images/shimano_reels/Sephia BB_main.jpg</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2708,7 +2708,7 @@
         <v>SRE1048</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="str">
         <v>EXSENCE BB</v>
@@ -2732,10 +2732,10 @@
         <v>images/shimano_reels/EXSENCE BB_main.jpg</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2755,7 +2755,7 @@
         <v>SRE1049</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="str">
         <v>AERO XR</v>
@@ -2779,10 +2779,10 @@
         <v>images/shimano_reels/AERO XR_main.jpg</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2802,7 +2802,7 @@
         <v>SRE1050</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="str">
         <v>ULTEGRA</v>
@@ -2826,10 +2826,10 @@
         <v>images/shimano_reels/ULTEGRA_main.jpg</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2849,7 +2849,7 @@
         <v>SRE1051</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="str">
         <v>Soare BB</v>
@@ -2873,10 +2873,10 @@
         <v>images/shimano_reels/Soare BB_main.jpg</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2896,7 +2896,7 @@
         <v>SRE1052</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="str">
         <v>AERLEX XTC</v>
@@ -2920,10 +2920,10 @@
         <v>images/shimano_reels/AERLEX XTC_main.jpg</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2943,7 +2943,7 @@
         <v>SRE1053</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="str">
         <v>AERLEX XSC</v>
@@ -2967,10 +2967,10 @@
         <v>images/shimano_reels/AERLEX XSC_main.jpg</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2990,7 +2990,7 @@
         <v>SRE1054</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="str">
         <v>AERO</v>
@@ -3014,10 +3014,10 @@
         <v>images/shimano_reels/AERO_main.jpg</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -3037,7 +3037,7 @@
         <v>SRE1055</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="str">
         <v>MIRAVEL</v>
@@ -3061,10 +3061,10 @@
         <v>images/shimano_reels/MIRAVEL_main.jpg</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -3084,7 +3084,7 @@
         <v>SRE1056</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="str">
         <v>NASCI</v>
@@ -3108,10 +3108,10 @@
         <v>images/shimano_reels/NASCI_main.jpg</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -3131,7 +3131,7 @@
         <v>SRE1057</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="str">
         <v>SOCORRO SW</v>
@@ -3155,10 +3155,10 @@
         <v>images/shimano_reels/SOCORRO SW_main.jpg</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -3178,7 +3178,7 @@
         <v>SRE1058</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="str">
         <v>AERO BB</v>
@@ -3202,10 +3202,10 @@
         <v>images/shimano_reels/AERO BB_main.jpg</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -3225,7 +3225,7 @@
         <v>SRE1059</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="str">
         <v>SAHARA</v>
@@ -3249,10 +3249,10 @@
         <v>images/shimano_reels/SAHARA_main.jpg</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -3272,7 +3272,7 @@
         <v>SRE1060</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="str">
         <v>ACTIVECAST</v>
@@ -3296,10 +3296,10 @@
         <v>images/shimano_reels/ACTIVECAST_main.jpg</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3319,7 +3319,7 @@
         <v>SRE1061</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" t="str">
         <v>SEDONA</v>
@@ -3343,10 +3343,10 @@
         <v>images/shimano_reels/SEDONA_main.jpg</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3366,7 +3366,7 @@
         <v>SRE1062</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" t="str">
         <v>ALIVIO</v>
@@ -3390,10 +3390,10 @@
         <v>images/shimano_reels/ALIVIO_main.jpg</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3413,7 +3413,7 @@
         <v>SRE1063</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="str">
         <v>NEXAVE</v>
@@ -3437,10 +3437,10 @@
         <v>images/shimano_reels/NEXAVE_main.jpg</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3460,7 +3460,7 @@
         <v>SRE1064</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="str">
         <v>CATANA</v>
@@ -3484,10 +3484,10 @@
         <v>images/shimano_reels/CATANA_main.jpg</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3507,7 +3507,7 @@
         <v>SRE1065</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" t="str">
         <v>SIENNA</v>
@@ -3531,10 +3531,10 @@
         <v>images/shimano_reels/SIENNA_main.jpg</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3554,7 +3554,7 @@
         <v>SRE1066</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="str">
         <v>FX</v>
@@ -3578,10 +3578,10 @@
         <v>images/shimano_reels/FX_main.jpg</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3693,7 +3693,7 @@
         <v>handle_style</v>
       </c>
       <c r="AC1" t="str">
-        <v>MAX DURABILITY</v>
+        <v>MAX_DURABILITY</v>
       </c>
     </row>
     <row r="2">
@@ -3752,10 +3752,10 @@
         <v>047472</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U2" t="str">
         <v/>
@@ -3841,10 +3841,10 @@
         <v>047489</v>
       </c>
       <c r="S3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U3" t="str">
         <v/>
@@ -3930,10 +3930,10 @@
         <v>047496</v>
       </c>
       <c r="S4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U4" t="str">
         <v/>
@@ -4019,10 +4019,10 @@
         <v>047502</v>
       </c>
       <c r="S5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U5" t="str">
         <v/>
@@ -4108,10 +4108,10 @@
         <v>047519</v>
       </c>
       <c r="S6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U6" t="str">
         <v/>
@@ -4197,10 +4197,10 @@
         <v>047526</v>
       </c>
       <c r="S7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U7" t="str">
         <v/>
@@ -4286,10 +4286,10 @@
         <v>047533</v>
       </c>
       <c r="S8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U8" t="str">
         <v/>
@@ -4375,10 +4375,10 @@
         <v>047540</v>
       </c>
       <c r="S9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U9" t="str">
         <v/>
@@ -4464,10 +4464,10 @@
         <v>047557</v>
       </c>
       <c r="S10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U10" t="str">
         <v/>
@@ -4553,10 +4553,10 @@
         <v>047564</v>
       </c>
       <c r="S11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U11" t="str">
         <v/>
@@ -4642,10 +4642,10 @@
         <v>047571</v>
       </c>
       <c r="S12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U12" t="str">
         <v/>
@@ -4731,10 +4731,10 @@
         <v>047588</v>
       </c>
       <c r="S13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U13" t="str">
         <v/>
@@ -4820,10 +4820,10 @@
         <v>047595</v>
       </c>
       <c r="S14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U14" t="str">
         <v/>
@@ -4909,10 +4909,10 @@
         <v>047601</v>
       </c>
       <c r="S15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U15" t="str">
         <v/>
@@ -4998,10 +4998,10 @@
         <v>047618</v>
       </c>
       <c r="S16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U16" t="str">
         <v/>
@@ -5087,10 +5087,10 @@
         <v>047625</v>
       </c>
       <c r="S17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U17" t="str">
         <v/>
@@ -5176,10 +5176,10 @@
         <v>048059</v>
       </c>
       <c r="S18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U18" t="str">
         <v/>
@@ -5265,10 +5265,10 @@
         <v>041289</v>
       </c>
       <c r="S19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U19" t="str">
         <v/>
@@ -5354,10 +5354,10 @@
         <v>040824</v>
       </c>
       <c r="S20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U20" t="str">
         <v/>
@@ -5443,10 +5443,10 @@
         <v>047793</v>
       </c>
       <c r="S21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U21" t="str">
         <v/>
@@ -5532,10 +5532,10 @@
         <v>047809</v>
       </c>
       <c r="S22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U22" t="str">
         <v/>
@@ -5621,10 +5621,10 @@
         <v>047816</v>
       </c>
       <c r="S23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U23" t="str">
         <v/>
@@ -5710,10 +5710,10 @@
         <v>047823</v>
       </c>
       <c r="S24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U24" t="str">
         <v/>
@@ -5799,10 +5799,10 @@
         <v>043528</v>
       </c>
       <c r="S25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U25" t="str">
         <v/>
@@ -5888,10 +5888,10 @@
         <v>043535</v>
       </c>
       <c r="S26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U26" t="str">
         <v/>
@@ -5977,10 +5977,10 @@
         <v>043542</v>
       </c>
       <c r="S27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U27" t="str">
         <v/>
@@ -6066,10 +6066,10 @@
         <v>043559</v>
       </c>
       <c r="S28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U28" t="str">
         <v/>
@@ -6155,10 +6155,10 @@
         <v>043566</v>
       </c>
       <c r="S29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U29" t="str">
         <v/>
@@ -6244,10 +6244,10 @@
         <v>044341</v>
       </c>
       <c r="S30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U30" t="str">
         <v/>
@@ -6333,10 +6333,10 @@
         <v>044358</v>
       </c>
       <c r="S31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U31" t="str">
         <v/>
@@ -6422,10 +6422,10 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U32" t="str">
         <v/>
@@ -6511,10 +6511,10 @@
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U33" t="str">
         <v/>
@@ -6600,10 +6600,10 @@
         <v>-</v>
       </c>
       <c r="S34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U34" t="str">
         <v/>
@@ -6689,10 +6689,10 @@
         <v>043825</v>
       </c>
       <c r="S35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U35" t="str">
         <v/>
@@ -6778,10 +6778,10 @@
         <v>043832</v>
       </c>
       <c r="S36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U36" t="str">
         <v/>
@@ -6867,10 +6867,10 @@
         <v>043849</v>
       </c>
       <c r="S37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U37" t="str">
         <v/>
@@ -6956,10 +6956,10 @@
         <v>043856</v>
       </c>
       <c r="S38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U38" t="str">
         <v/>
@@ -7045,10 +7045,10 @@
         <v>043863</v>
       </c>
       <c r="S39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U39" t="str">
         <v/>
@@ -7134,10 +7134,10 @@
         <v>-</v>
       </c>
       <c r="S40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U40" t="str">
         <v/>
@@ -7223,10 +7223,10 @@
         <v>-</v>
       </c>
       <c r="S41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U41" t="str">
         <v/>
@@ -7312,10 +7312,10 @@
         <v>043870</v>
       </c>
       <c r="S42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U42" t="str">
         <v/>
@@ -7401,10 +7401,10 @@
         <v>043887</v>
       </c>
       <c r="S43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U43" t="str">
         <v/>
@@ -7490,10 +7490,10 @@
         <v>-</v>
       </c>
       <c r="S44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U44" t="str">
         <v/>
@@ -7579,10 +7579,10 @@
         <v>043894</v>
       </c>
       <c r="S45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U45" t="str">
         <v/>
@@ -7668,10 +7668,10 @@
         <v>043900</v>
       </c>
       <c r="S46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U46" t="str">
         <v/>
@@ -7757,10 +7757,10 @@
         <v>043917</v>
       </c>
       <c r="S47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U47" t="str">
         <v/>
@@ -7846,10 +7846,10 @@
         <v>043924</v>
       </c>
       <c r="S48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U48" t="str">
         <v/>
@@ -7935,10 +7935,10 @@
         <v>043931</v>
       </c>
       <c r="S49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U49" t="str">
         <v/>
@@ -8024,10 +8024,10 @@
         <v>043948</v>
       </c>
       <c r="S50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U50" t="str">
         <v/>
@@ -8113,10 +8113,10 @@
         <v>043955</v>
       </c>
       <c r="S51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U51" t="str">
         <v/>
@@ -8202,10 +8202,10 @@
         <v>043962</v>
       </c>
       <c r="S52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U52" t="str">
         <v/>
@@ -8291,10 +8291,10 @@
         <v>043979</v>
       </c>
       <c r="S53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U53" t="str">
         <v/>
@@ -8380,10 +8380,10 @@
         <v>-</v>
       </c>
       <c r="S54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U54" t="str">
         <v/>
@@ -8469,10 +8469,10 @@
         <v>048202</v>
       </c>
       <c r="S55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U55" t="str">
         <v/>
@@ -8558,10 +8558,10 @@
         <v>048219</v>
       </c>
       <c r="S56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U56" t="str">
         <v/>
@@ -8647,10 +8647,10 @@
         <v>048226</v>
       </c>
       <c r="S57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U57" t="str">
         <v/>
@@ -8736,10 +8736,10 @@
         <v>042217</v>
       </c>
       <c r="S58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U58" t="str">
         <v/>
@@ -8825,10 +8825,10 @@
         <v>042224</v>
       </c>
       <c r="S59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U59" t="str">
         <v/>
@@ -8914,10 +8914,10 @@
         <v>042231</v>
       </c>
       <c r="S60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U60" t="str">
         <v/>
@@ -9003,10 +9003,10 @@
         <v>042248</v>
       </c>
       <c r="S61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U61" t="str">
         <v/>
@@ -9092,10 +9092,10 @@
         <v>042255</v>
       </c>
       <c r="S62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U62" t="str">
         <v/>
@@ -9181,10 +9181,10 @@
         <v>042262</v>
       </c>
       <c r="S63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U63" t="str">
         <v/>
@@ -9270,10 +9270,10 @@
         <v>042279</v>
       </c>
       <c r="S64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U64" t="str">
         <v/>
@@ -9359,10 +9359,10 @@
         <v>042286</v>
       </c>
       <c r="S65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U65" t="str">
         <v/>
@@ -9448,10 +9448,10 @@
         <v>042293</v>
       </c>
       <c r="S66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U66" t="str">
         <v/>
@@ -9537,10 +9537,10 @@
         <v>042309</v>
       </c>
       <c r="S67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U67" t="str">
         <v/>
@@ -9626,10 +9626,10 @@
         <v>043511</v>
       </c>
       <c r="S68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U68" t="str">
         <v/>
@@ -9715,10 +9715,10 @@
         <v>042316</v>
       </c>
       <c r="S69" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T69" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U69" t="str">
         <v/>
@@ -9804,10 +9804,10 @@
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T70" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U70" t="str">
         <v/>
@@ -9893,10 +9893,10 @@
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T71" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U71" t="str">
         <v/>
@@ -9982,10 +9982,10 @@
         <v/>
       </c>
       <c r="S72" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T72" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U72" t="str">
         <v/>
@@ -10071,10 +10071,10 @@
         <v>049025</v>
       </c>
       <c r="S73" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T73" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U73" t="str">
         <v/>
@@ -10160,10 +10160,10 @@
         <v>049032</v>
       </c>
       <c r="S74" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T74" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U74" t="str">
         <v/>
@@ -10249,10 +10249,10 @@
         <v>049049</v>
       </c>
       <c r="S75" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T75" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U75" t="str">
         <v/>
@@ -10338,10 +10338,10 @@
         <v>049056</v>
       </c>
       <c r="S76" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T76" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U76" t="str">
         <v/>
@@ -10427,10 +10427,10 @@
         <v>043429</v>
       </c>
       <c r="S77" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T77" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U77" t="str">
         <v/>
@@ -10516,10 +10516,10 @@
         <v>047243</v>
       </c>
       <c r="S78" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T78" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U78" t="str">
         <v/>
@@ -10605,10 +10605,10 @@
         <v>047250</v>
       </c>
       <c r="S79" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T79" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U79" t="str">
         <v/>
@@ -10694,10 +10694,10 @@
         <v>047267</v>
       </c>
       <c r="S80" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T80" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U80" t="str">
         <v/>
@@ -10783,10 +10783,10 @@
         <v>049247</v>
       </c>
       <c r="S81" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T81" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U81" t="str">
         <v/>
@@ -10872,10 +10872,10 @@
         <v>049254</v>
       </c>
       <c r="S82" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T82" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U82" t="str">
         <v/>
@@ -10961,10 +10961,10 @@
         <v>049261</v>
       </c>
       <c r="S83" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T83" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U83" t="str">
         <v/>
@@ -11050,10 +11050,10 @@
         <v>049278</v>
       </c>
       <c r="S84" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T84" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U84" t="str">
         <v/>
@@ -11139,10 +11139,10 @@
         <v>049285</v>
       </c>
       <c r="S85" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T85" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U85" t="str">
         <v/>
@@ -11228,10 +11228,10 @@
         <v>049292</v>
       </c>
       <c r="S86" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T86" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U86" t="str">
         <v/>
@@ -11317,10 +11317,10 @@
         <v>049308</v>
       </c>
       <c r="S87" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T87" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U87" t="str">
         <v/>
@@ -11406,10 +11406,10 @@
         <v>049315</v>
       </c>
       <c r="S88" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T88" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U88" t="str">
         <v/>
@@ -11495,10 +11495,10 @@
         <v>045225</v>
       </c>
       <c r="S89" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T89" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U89" t="str">
         <v/>
@@ -11584,10 +11584,10 @@
         <v>045232</v>
       </c>
       <c r="S90" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T90" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U90" t="str">
         <v/>
@@ -11673,10 +11673,10 @@
         <v>045249</v>
       </c>
       <c r="S91" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T91" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U91" t="str">
         <v/>
@@ -11762,10 +11762,10 @@
         <v>045256</v>
       </c>
       <c r="S92" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T92" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U92" t="str">
         <v/>
@@ -11851,10 +11851,10 @@
         <v>045263</v>
       </c>
       <c r="S93" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T93" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U93" t="str">
         <v/>
@@ -11940,10 +11940,10 @@
         <v>045270</v>
       </c>
       <c r="S94" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T94" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U94" t="str">
         <v/>
@@ -12029,10 +12029,10 @@
         <v>045287</v>
       </c>
       <c r="S95" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T95" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U95" t="str">
         <v/>
@@ -12118,10 +12118,10 @@
         <v>045294</v>
       </c>
       <c r="S96" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T96" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U96" t="str">
         <v/>
@@ -12207,10 +12207,10 @@
         <v>045300</v>
       </c>
       <c r="S97" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T97" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U97" t="str">
         <v/>
@@ -12296,10 +12296,10 @@
         <v>045317</v>
       </c>
       <c r="S98" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T98" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U98" t="str">
         <v/>
@@ -12385,10 +12385,10 @@
         <v>045324</v>
       </c>
       <c r="S99" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T99" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U99" t="str">
         <v/>
@@ -12474,10 +12474,10 @@
         <v>045331</v>
       </c>
       <c r="S100" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T100" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U100" t="str">
         <v/>
@@ -12563,10 +12563,10 @@
         <v>045348</v>
       </c>
       <c r="S101" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T101" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U101" t="str">
         <v/>
@@ -12652,10 +12652,10 @@
         <v>045355</v>
       </c>
       <c r="S102" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T102" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U102" t="str">
         <v/>
@@ -12741,10 +12741,10 @@
         <v>045362</v>
       </c>
       <c r="S103" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T103" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U103" t="str">
         <v/>
@@ -12830,10 +12830,10 @@
         <v/>
       </c>
       <c r="S104" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T104" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U104" t="str">
         <v/>
@@ -12919,10 +12919,10 @@
         <v/>
       </c>
       <c r="S105" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T105" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U105" t="str">
         <v/>
@@ -13008,10 +13008,10 @@
         <v/>
       </c>
       <c r="S106" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T106" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U106" t="str">
         <v/>
@@ -13097,10 +13097,10 @@
         <v/>
       </c>
       <c r="S107" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T107" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U107" t="str">
         <v/>
@@ -13186,10 +13186,10 @@
         <v/>
       </c>
       <c r="S108" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T108" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U108" t="str">
         <v/>
@@ -13275,10 +13275,10 @@
         <v/>
       </c>
       <c r="S109" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T109" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U109" t="str">
         <v/>
@@ -13364,10 +13364,10 @@
         <v/>
       </c>
       <c r="S110" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T110" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U110" t="str">
         <v/>
@@ -13453,10 +13453,10 @@
         <v/>
       </c>
       <c r="S111" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T111" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U111" t="str">
         <v/>
@@ -13542,10 +13542,10 @@
         <v>044884</v>
       </c>
       <c r="S112" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T112" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U112" t="str">
         <v/>
@@ -13631,10 +13631,10 @@
         <v>044891</v>
       </c>
       <c r="S113" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T113" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U113" t="str">
         <v/>
@@ -13720,10 +13720,10 @@
         <v>044907</v>
       </c>
       <c r="S114" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T114" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U114" t="str">
         <v/>
@@ -13809,10 +13809,10 @@
         <v>044914</v>
       </c>
       <c r="S115" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T115" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U115" t="str">
         <v/>
@@ -13898,10 +13898,10 @@
         <v>044921</v>
       </c>
       <c r="S116" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T116" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U116" t="str">
         <v/>
@@ -13987,10 +13987,10 @@
         <v>044938</v>
       </c>
       <c r="S117" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T117" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U117" t="str">
         <v/>
@@ -14076,10 +14076,10 @@
         <v>044945</v>
       </c>
       <c r="S118" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T118" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U118" t="str">
         <v/>
@@ -14165,10 +14165,10 @@
         <v>039392</v>
       </c>
       <c r="S119" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T119" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U119" t="str">
         <v/>
@@ -14254,10 +14254,10 @@
         <v>039408</v>
       </c>
       <c r="S120" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T120" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U120" t="str">
         <v/>
@@ -14343,10 +14343,10 @@
         <v>039415</v>
       </c>
       <c r="S121" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T121" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U121" t="str">
         <v/>
@@ -14432,10 +14432,10 @@
         <v>046765</v>
       </c>
       <c r="S122" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T122" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U122" t="str">
         <v/>
@@ -14521,10 +14521,10 @@
         <v>046772</v>
       </c>
       <c r="S123" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T123" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U123" t="str">
         <v/>
@@ -14610,10 +14610,10 @@
         <v>049216</v>
       </c>
       <c r="S124" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T124" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U124" t="str">
         <v/>
@@ -14699,10 +14699,10 @@
         <v>-</v>
       </c>
       <c r="S125" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T125" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U125" t="str">
         <v/>
@@ -14788,10 +14788,10 @@
         <v>046789</v>
       </c>
       <c r="S126" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T126" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U126" t="str">
         <v/>
@@ -14877,10 +14877,10 @@
         <v>046796</v>
       </c>
       <c r="S127" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T127" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U127" t="str">
         <v/>
@@ -14966,10 +14966,10 @@
         <v>046802</v>
       </c>
       <c r="S128" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T128" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U128" t="str">
         <v/>
@@ -15055,10 +15055,10 @@
         <v>046819</v>
       </c>
       <c r="S129" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T129" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U129" t="str">
         <v/>
@@ -15144,10 +15144,10 @@
         <v>046826</v>
       </c>
       <c r="S130" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T130" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U130" t="str">
         <v/>
@@ -15233,10 +15233,10 @@
         <v>046833</v>
       </c>
       <c r="S131" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T131" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U131" t="str">
         <v/>
@@ -15322,10 +15322,10 @@
         <v>046840</v>
       </c>
       <c r="S132" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T132" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U132" t="str">
         <v/>
@@ -15411,10 +15411,10 @@
         <v>046857</v>
       </c>
       <c r="S133" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T133" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U133" t="str">
         <v/>
@@ -15500,10 +15500,10 @@
         <v>046864</v>
       </c>
       <c r="S134" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T134" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U134" t="str">
         <v/>
@@ -15589,10 +15589,10 @@
         <v>046871</v>
       </c>
       <c r="S135" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T135" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U135" t="str">
         <v/>
@@ -15678,10 +15678,10 @@
         <v>046888</v>
       </c>
       <c r="S136" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T136" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U136" t="str">
         <v/>
@@ -15767,10 +15767,10 @@
         <v>047885</v>
       </c>
       <c r="S137" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T137" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U137" t="str">
         <v/>
@@ -15856,10 +15856,10 @@
         <v>047892</v>
       </c>
       <c r="S138" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T138" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U138" t="str">
         <v/>
@@ -15945,10 +15945,10 @@
         <v>047908</v>
       </c>
       <c r="S139" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T139" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U139" t="str">
         <v/>
@@ -16034,10 +16034,10 @@
         <v>047915</v>
       </c>
       <c r="S140" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T140" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U140" t="str">
         <v/>
@@ -16123,10 +16123,10 @@
         <v>047922</v>
       </c>
       <c r="S141" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T141" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U141" t="str">
         <v/>
@@ -16212,10 +16212,10 @@
         <v>047939</v>
       </c>
       <c r="S142" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T142" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U142" t="str">
         <v/>
@@ -16301,10 +16301,10 @@
         <v>046239</v>
       </c>
       <c r="S143" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T143" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U143" t="str">
         <v/>
@@ -16390,10 +16390,10 @@
         <v>046246</v>
       </c>
       <c r="S144" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T144" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U144" t="str">
         <v/>
@@ -16479,10 +16479,10 @@
         <v>046253</v>
       </c>
       <c r="S145" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T145" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U145" t="str">
         <v/>
@@ -16568,10 +16568,10 @@
         <v>046086</v>
       </c>
       <c r="S146" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T146" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U146" t="str">
         <v/>
@@ -16657,10 +16657,10 @@
         <v>046093</v>
       </c>
       <c r="S147" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T147" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U147" t="str">
         <v/>
@@ -16746,10 +16746,10 @@
         <v>046109</v>
       </c>
       <c r="S148" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T148" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U148" t="str">
         <v/>
@@ -16835,10 +16835,10 @@
         <v/>
       </c>
       <c r="S149" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T149" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U149" t="str">
         <v/>
@@ -16924,10 +16924,10 @@
         <v/>
       </c>
       <c r="S150" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T150" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U150" t="str">
         <v/>
@@ -17013,10 +17013,10 @@
         <v>042781</v>
       </c>
       <c r="S151" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T151" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U151" t="str">
         <v/>
@@ -17102,10 +17102,10 @@
         <v>042798</v>
       </c>
       <c r="S152" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T152" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U152" t="str">
         <v/>
@@ -17191,10 +17191,10 @@
         <v>042804</v>
       </c>
       <c r="S153" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T153" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U153" t="str">
         <v/>
@@ -17280,10 +17280,10 @@
         <v>042811</v>
       </c>
       <c r="S154" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T154" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U154" t="str">
         <v/>
@@ -17369,10 +17369,10 @@
         <v>045003</v>
       </c>
       <c r="S155" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T155" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U155" t="str">
         <v/>
@@ -17458,10 +17458,10 @@
         <v>046154</v>
       </c>
       <c r="S156" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T156" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U156" t="str">
         <v/>
@@ -17547,10 +17547,10 @@
         <v>046161</v>
       </c>
       <c r="S157" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T157" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U157" t="str">
         <v/>
@@ -17636,10 +17636,10 @@
         <v>046178</v>
       </c>
       <c r="S158" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T158" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U158" t="str">
         <v/>
@@ -17725,10 +17725,10 @@
         <v>046185</v>
       </c>
       <c r="S159" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T159" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U159" t="str">
         <v/>
@@ -17814,10 +17814,10 @@
         <v>045676</v>
       </c>
       <c r="S160" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T160" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U160" t="str">
         <v/>
@@ -17903,10 +17903,10 @@
         <v>048905</v>
       </c>
       <c r="S161" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T161" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U161" t="str">
         <v/>
@@ -17992,10 +17992,10 @@
         <v>048912</v>
       </c>
       <c r="S162" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T162" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U162" t="str">
         <v/>
@@ -18081,10 +18081,10 @@
         <v>048929</v>
       </c>
       <c r="S163" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T163" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U163" t="str">
         <v/>
@@ -18170,10 +18170,10 @@
         <v>048936</v>
       </c>
       <c r="S164" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T164" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U164" t="str">
         <v/>
@@ -18259,10 +18259,10 @@
         <v>048943</v>
       </c>
       <c r="S165" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T165" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U165" t="str">
         <v/>
@@ -18348,10 +18348,10 @@
         <v>047373</v>
       </c>
       <c r="S166" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T166" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U166" t="str">
         <v/>
@@ -18437,10 +18437,10 @@
         <v>047380</v>
       </c>
       <c r="S167" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T167" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U167" t="str">
         <v/>
@@ -18526,10 +18526,10 @@
         <v>047397</v>
       </c>
       <c r="S168" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T168" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U168" t="str">
         <v/>
@@ -18615,10 +18615,10 @@
         <v>047403</v>
       </c>
       <c r="S169" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T169" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U169" t="str">
         <v/>
@@ -18704,10 +18704,10 @@
         <v>047410</v>
       </c>
       <c r="S170" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T170" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U170" t="str">
         <v/>
@@ -18793,10 +18793,10 @@
         <v>047427</v>
       </c>
       <c r="S171" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T171" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U171" t="str">
         <v/>
@@ -18882,10 +18882,10 @@
         <v>047434</v>
       </c>
       <c r="S172" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T172" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U172" t="str">
         <v/>
@@ -18971,10 +18971,10 @@
         <v>047441</v>
       </c>
       <c r="S173" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T173" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U173" t="str">
         <v/>
@@ -19060,10 +19060,10 @@
         <v>047458</v>
       </c>
       <c r="S174" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T174" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U174" t="str">
         <v/>
@@ -19149,10 +19149,10 @@
         <v/>
       </c>
       <c r="S175" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T175" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U175" t="str">
         <v/>
@@ -19238,10 +19238,10 @@
         <v/>
       </c>
       <c r="S176" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T176" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U176" t="str">
         <v/>
@@ -19327,10 +19327,10 @@
         <v/>
       </c>
       <c r="S177" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T177" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U177" t="str">
         <v/>
@@ -19416,10 +19416,10 @@
         <v/>
       </c>
       <c r="S178" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T178" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U178" t="str">
         <v/>
@@ -19505,10 +19505,10 @@
         <v/>
       </c>
       <c r="S179" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T179" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U179" t="str">
         <v/>
@@ -19594,10 +19594,10 @@
         <v/>
       </c>
       <c r="S180" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T180" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U180" t="str">
         <v/>
@@ -19683,10 +19683,10 @@
         <v/>
       </c>
       <c r="S181" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T181" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U181" t="str">
         <v/>
@@ -19772,10 +19772,10 @@
         <v>048950</v>
       </c>
       <c r="S182" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T182" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U182" t="str">
         <v/>
@@ -19861,10 +19861,10 @@
         <v>048967</v>
       </c>
       <c r="S183" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T183" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U183" t="str">
         <v/>
@@ -19950,10 +19950,10 @@
         <v>048974</v>
       </c>
       <c r="S184" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T184" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U184" t="str">
         <v/>
@@ -20039,10 +20039,10 @@
         <v>048981</v>
       </c>
       <c r="S185" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T185" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U185" t="str">
         <v/>
@@ -20128,10 +20128,10 @@
         <v>046550</v>
       </c>
       <c r="S186" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T186" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U186" t="str">
         <v/>
@@ -20217,10 +20217,10 @@
         <v>046567</v>
       </c>
       <c r="S187" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T187" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U187" t="str">
         <v/>
@@ -20306,10 +20306,10 @@
         <v>046048</v>
       </c>
       <c r="S188" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T188" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U188" t="str">
         <v/>
@@ -20395,10 +20395,10 @@
         <v>046055</v>
       </c>
       <c r="S189" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T189" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U189" t="str">
         <v/>
@@ -20484,10 +20484,10 @@
         <v>046062</v>
       </c>
       <c r="S190" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T190" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U190" t="str">
         <v/>
@@ -20573,10 +20573,10 @@
         <v>046079</v>
       </c>
       <c r="S191" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T191" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U191" t="str">
         <v/>
@@ -20662,10 +20662,10 @@
         <v>032713</v>
       </c>
       <c r="S192" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T192" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U192" t="str">
         <v/>
@@ -20751,10 +20751,10 @@
         <v>032720</v>
       </c>
       <c r="S193" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T193" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U193" t="str">
         <v/>
@@ -20840,10 +20840,10 @@
         <v>032737</v>
       </c>
       <c r="S194" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T194" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U194" t="str">
         <v/>
@@ -20929,10 +20929,10 @@
         <v>032744</v>
       </c>
       <c r="S195" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T195" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U195" t="str">
         <v/>
@@ -21018,10 +21018,10 @@
         <v>048424</v>
       </c>
       <c r="S196" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T196" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U196" t="str">
         <v/>
@@ -21107,10 +21107,10 @@
         <v>048431</v>
       </c>
       <c r="S197" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T197" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U197" t="str">
         <v/>
@@ -21196,10 +21196,10 @@
         <v>048448</v>
       </c>
       <c r="S198" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T198" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U198" t="str">
         <v/>
@@ -21285,10 +21285,10 @@
         <v>048455</v>
       </c>
       <c r="S199" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T199" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U199" t="str">
         <v/>
@@ -21374,10 +21374,10 @@
         <v>044297</v>
       </c>
       <c r="S200" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T200" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U200" t="str">
         <v/>
@@ -21463,10 +21463,10 @@
         <v/>
       </c>
       <c r="S201" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T201" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U201" t="str">
         <v/>
@@ -21552,10 +21552,10 @@
         <v/>
       </c>
       <c r="S202" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T202" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U202" t="str">
         <v/>
@@ -21641,10 +21641,10 @@
         <v>048288</v>
       </c>
       <c r="S203" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T203" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U203" t="str">
         <v/>
@@ -21730,10 +21730,10 @@
         <v>048295</v>
       </c>
       <c r="S204" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T204" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U204" t="str">
         <v/>
@@ -21819,10 +21819,10 @@
         <v>048301</v>
       </c>
       <c r="S205" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T205" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U205" t="str">
         <v/>
@@ -21908,10 +21908,10 @@
         <v>046307</v>
       </c>
       <c r="S206" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T206" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U206" t="str">
         <v/>
@@ -21997,10 +21997,10 @@
         <v>046314</v>
       </c>
       <c r="S207" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T207" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U207" t="str">
         <v/>
@@ -22086,10 +22086,10 @@
         <v>046321</v>
       </c>
       <c r="S208" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T208" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U208" t="str">
         <v/>
@@ -22175,10 +22175,10 @@
         <v>046338</v>
       </c>
       <c r="S209" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T209" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U209" t="str">
         <v/>
@@ -22264,10 +22264,10 @@
         <v>-</v>
       </c>
       <c r="S210" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T210" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U210" t="str">
         <v/>
@@ -22353,10 +22353,10 @@
         <v>047014</v>
       </c>
       <c r="S211" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T211" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U211" t="str">
         <v/>
@@ -22442,10 +22442,10 @@
         <v>047021</v>
       </c>
       <c r="S212" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T212" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U212" t="str">
         <v/>
@@ -22531,10 +22531,10 @@
         <v>-</v>
       </c>
       <c r="S213" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T213" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U213" t="str">
         <v/>
@@ -22620,10 +22620,10 @@
         <v>047038</v>
       </c>
       <c r="S214" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T214" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U214" t="str">
         <v/>
@@ -22709,10 +22709,10 @@
         <v>047045</v>
       </c>
       <c r="S215" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T215" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U215" t="str">
         <v/>
@@ -22798,10 +22798,10 @@
         <v>047052</v>
       </c>
       <c r="S216" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T216" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U216" t="str">
         <v/>
@@ -22887,10 +22887,10 @@
         <v>047069</v>
       </c>
       <c r="S217" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T217" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U217" t="str">
         <v/>
@@ -22976,10 +22976,10 @@
         <v>-</v>
       </c>
       <c r="S218" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T218" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U218" t="str">
         <v/>
@@ -23065,10 +23065,10 @@
         <v>-</v>
       </c>
       <c r="S219" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T219" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U219" t="str">
         <v/>
@@ -23154,10 +23154,10 @@
         <v>047090</v>
       </c>
       <c r="S220" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T220" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U220" t="str">
         <v/>
@@ -23243,10 +23243,10 @@
         <v>-</v>
       </c>
       <c r="S221" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T221" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U221" t="str">
         <v/>
@@ -23332,10 +23332,10 @@
         <v>047076</v>
       </c>
       <c r="S222" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T222" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U222" t="str">
         <v/>
@@ -23421,10 +23421,10 @@
         <v>047083</v>
       </c>
       <c r="S223" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T223" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U223" t="str">
         <v/>
@@ -23510,10 +23510,10 @@
         <v>047106</v>
       </c>
       <c r="S224" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T224" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U224" t="str">
         <v/>
@@ -23599,10 +23599,10 @@
         <v>-</v>
       </c>
       <c r="S225" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T225" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U225" t="str">
         <v/>
@@ -23688,10 +23688,10 @@
         <v>047113</v>
       </c>
       <c r="S226" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T226" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U226" t="str">
         <v/>
@@ -23777,10 +23777,10 @@
         <v>047120</v>
       </c>
       <c r="S227" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T227" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U227" t="str">
         <v/>
@@ -23866,10 +23866,10 @@
         <v>047137</v>
       </c>
       <c r="S228" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T228" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U228" t="str">
         <v/>
@@ -23955,10 +23955,10 @@
         <v/>
       </c>
       <c r="S229" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T229" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U229" t="str">
         <v/>
@@ -24044,10 +24044,10 @@
         <v/>
       </c>
       <c r="S230" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T230" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U230" t="str">
         <v/>
@@ -24133,10 +24133,10 @@
         <v>046192</v>
       </c>
       <c r="S231" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T231" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U231" t="str">
         <v/>
@@ -24222,10 +24222,10 @@
         <v>046208</v>
       </c>
       <c r="S232" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T232" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U232" t="str">
         <v/>
@@ -24311,10 +24311,10 @@
         <v>046215</v>
       </c>
       <c r="S233" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T233" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U233" t="str">
         <v/>
@@ -24400,10 +24400,10 @@
         <v>046222</v>
       </c>
       <c r="S234" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T234" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U234" t="str">
         <v/>
@@ -24489,10 +24489,10 @@
         <v>-</v>
       </c>
       <c r="S235" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T235" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U235" t="str">
         <v/>
@@ -24578,10 +24578,10 @@
         <v>-</v>
       </c>
       <c r="S236" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T236" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U236" t="str">
         <v/>
@@ -24667,10 +24667,10 @@
         <v>-</v>
       </c>
       <c r="S237" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T237" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U237" t="str">
         <v/>
@@ -24756,10 +24756,10 @@
         <v>-</v>
       </c>
       <c r="S238" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T238" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U238" t="str">
         <v/>
@@ -24845,10 +24845,10 @@
         <v>-</v>
       </c>
       <c r="S239" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T239" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U239" t="str">
         <v/>
@@ -24934,10 +24934,10 @@
         <v>043610</v>
       </c>
       <c r="S240" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T240" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U240" t="str">
         <v/>
@@ -25023,10 +25023,10 @@
         <v>043627</v>
       </c>
       <c r="S241" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T241" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U241" t="str">
         <v/>
@@ -25112,10 +25112,10 @@
         <v>043634</v>
       </c>
       <c r="S242" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T242" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U242" t="str">
         <v/>
@@ -25201,10 +25201,10 @@
         <v>043641</v>
       </c>
       <c r="S243" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T243" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U243" t="str">
         <v/>
@@ -25290,10 +25290,10 @@
         <v>043658</v>
       </c>
       <c r="S244" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T244" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U244" t="str">
         <v/>
@@ -25379,10 +25379,10 @@
         <v/>
       </c>
       <c r="S245" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T245" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U245" t="str">
         <v/>
@@ -25468,10 +25468,10 @@
         <v>-</v>
       </c>
       <c r="S246" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T246" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U246" t="str">
         <v/>
@@ -25557,10 +25557,10 @@
         <v>-</v>
       </c>
       <c r="S247" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T247" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U247" t="str">
         <v/>
@@ -25646,10 +25646,10 @@
         <v>-</v>
       </c>
       <c r="S248" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T248" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U248" t="str">
         <v/>
@@ -25735,10 +25735,10 @@
         <v>045782</v>
       </c>
       <c r="S249" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T249" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U249" t="str">
         <v/>
@@ -25824,10 +25824,10 @@
         <v>045799</v>
       </c>
       <c r="S250" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T250" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U250" t="str">
         <v/>
@@ -25913,10 +25913,10 @@
         <v>045805</v>
       </c>
       <c r="S251" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T251" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U251" t="str">
         <v/>
@@ -26002,10 +26002,10 @@
         <v>045812</v>
       </c>
       <c r="S252" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T252" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U252" t="str">
         <v/>
@@ -26091,10 +26091,10 @@
         <v>-</v>
       </c>
       <c r="S253" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T253" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U253" t="str">
         <v/>
@@ -26180,10 +26180,10 @@
         <v>-</v>
       </c>
       <c r="S254" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T254" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U254" t="str">
         <v/>
@@ -26269,10 +26269,10 @@
         <v>045829</v>
       </c>
       <c r="S255" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T255" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U255" t="str">
         <v/>
@@ -26358,10 +26358,10 @@
         <v>045836</v>
       </c>
       <c r="S256" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T256" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U256" t="str">
         <v/>
@@ -26447,10 +26447,10 @@
         <v>045843</v>
       </c>
       <c r="S257" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T257" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U257" t="str">
         <v/>
@@ -26536,10 +26536,10 @@
         <v>045850</v>
       </c>
       <c r="S258" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T258" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U258" t="str">
         <v/>
@@ -26625,10 +26625,10 @@
         <v>045867</v>
       </c>
       <c r="S259" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T259" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U259" t="str">
         <v/>
@@ -26714,10 +26714,10 @@
         <v>045874</v>
       </c>
       <c r="S260" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T260" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U260" t="str">
         <v/>
@@ -26803,10 +26803,10 @@
         <v>045881</v>
       </c>
       <c r="S261" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T261" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U261" t="str">
         <v/>
@@ -26892,10 +26892,10 @@
         <v>045898</v>
       </c>
       <c r="S262" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T262" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U262" t="str">
         <v/>
@@ -26981,10 +26981,10 @@
         <v>045904</v>
       </c>
       <c r="S263" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T263" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U263" t="str">
         <v/>
@@ -27070,10 +27070,10 @@
         <v>045911</v>
       </c>
       <c r="S264" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T264" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U264" t="str">
         <v/>
@@ -27159,10 +27159,10 @@
         <v>032522</v>
       </c>
       <c r="S265" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T265" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U265" t="str">
         <v/>
@@ -27248,10 +27248,10 @@
         <v>032539</v>
       </c>
       <c r="S266" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T266" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U266" t="str">
         <v/>
@@ -27337,10 +27337,10 @@
         <v>032690</v>
       </c>
       <c r="S267" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T267" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U267" t="str">
         <v/>
@@ -27426,10 +27426,10 @@
         <v>032706</v>
       </c>
       <c r="S268" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T268" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U268" t="str">
         <v/>
@@ -27515,10 +27515,10 @@
         <v/>
       </c>
       <c r="S269" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T269" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U269" t="str">
         <v/>
@@ -27604,10 +27604,10 @@
         <v>045553</v>
       </c>
       <c r="S270" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T270" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U270" t="str">
         <v/>
@@ -27693,10 +27693,10 @@
         <v>045560</v>
       </c>
       <c r="S271" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T271" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U271" t="str">
         <v/>
@@ -27782,10 +27782,10 @@
         <v>045577</v>
       </c>
       <c r="S272" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T272" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U272" t="str">
         <v/>
@@ -27871,10 +27871,10 @@
         <v>045584</v>
       </c>
       <c r="S273" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T273" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U273" t="str">
         <v/>
@@ -27960,10 +27960,10 @@
         <v>047205</v>
       </c>
       <c r="S274" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T274" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U274" t="str">
         <v/>
@@ -28049,10 +28049,10 @@
         <v>047212</v>
       </c>
       <c r="S275" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T275" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U275" t="str">
         <v/>
@@ -28138,10 +28138,10 @@
         <v>047229</v>
       </c>
       <c r="S276" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T276" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U276" t="str">
         <v/>
@@ -28227,10 +28227,10 @@
         <v>047236</v>
       </c>
       <c r="S277" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T277" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U277" t="str">
         <v/>
@@ -28316,10 +28316,10 @@
         <v/>
       </c>
       <c r="S278" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T278" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U278" t="str">
         <v/>
@@ -28405,10 +28405,10 @@
         <v/>
       </c>
       <c r="S279" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T279" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U279" t="str">
         <v/>
@@ -28494,10 +28494,10 @@
         <v/>
       </c>
       <c r="S280" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T280" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U280" t="str">
         <v/>
@@ -28583,10 +28583,10 @@
         <v>-</v>
       </c>
       <c r="S281" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T281" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U281" t="str">
         <v/>
@@ -28672,10 +28672,10 @@
         <v>-</v>
       </c>
       <c r="S282" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T282" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U282" t="str">
         <v/>
@@ -28761,10 +28761,10 @@
         <v>047946</v>
       </c>
       <c r="S283" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T283" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U283" t="str">
         <v/>
@@ -28850,10 +28850,10 @@
         <v>047953</v>
       </c>
       <c r="S284" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T284" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U284" t="str">
         <v/>
@@ -28939,10 +28939,10 @@
         <v>047960</v>
       </c>
       <c r="S285" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T285" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U285" t="str">
         <v/>
@@ -29028,10 +29028,10 @@
         <v>047977</v>
       </c>
       <c r="S286" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T286" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U286" t="str">
         <v/>
@@ -29117,10 +29117,10 @@
         <v>-</v>
       </c>
       <c r="S287" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T287" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U287" t="str">
         <v/>
@@ -29206,10 +29206,10 @@
         <v>047984</v>
       </c>
       <c r="S288" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T288" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U288" t="str">
         <v/>
@@ -29295,10 +29295,10 @@
         <v>047991</v>
       </c>
       <c r="S289" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T289" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U289" t="str">
         <v/>
@@ -29384,10 +29384,10 @@
         <v>048004</v>
       </c>
       <c r="S290" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T290" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U290" t="str">
         <v/>
@@ -29473,10 +29473,10 @@
         <v>048011</v>
       </c>
       <c r="S291" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T291" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U291" t="str">
         <v/>
@@ -29562,10 +29562,10 @@
         <v>048028</v>
       </c>
       <c r="S292" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T292" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U292" t="str">
         <v/>
@@ -29651,10 +29651,10 @@
         <v>048035</v>
       </c>
       <c r="S293" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T293" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U293" t="str">
         <v/>
@@ -29740,10 +29740,10 @@
         <v>048042</v>
       </c>
       <c r="S294" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T294" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U294" t="str">
         <v/>
@@ -29829,10 +29829,10 @@
         <v>045737</v>
       </c>
       <c r="S295" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T295" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U295" t="str">
         <v/>
@@ -29918,10 +29918,10 @@
         <v>045744</v>
       </c>
       <c r="S296" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T296" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U296" t="str">
         <v/>
@@ -30007,10 +30007,10 @@
         <v>045751</v>
       </c>
       <c r="S297" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T297" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U297" t="str">
         <v/>
@@ -30096,10 +30096,10 @@
         <v/>
       </c>
       <c r="S298" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T298" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U298" t="str">
         <v/>
@@ -30185,10 +30185,10 @@
         <v/>
       </c>
       <c r="S299" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T299" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U299" t="str">
         <v/>
@@ -30274,10 +30274,10 @@
         <v/>
       </c>
       <c r="S300" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T300" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U300" t="str">
         <v/>
@@ -30363,10 +30363,10 @@
         <v/>
       </c>
       <c r="S301" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T301" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U301" t="str">
         <v/>
@@ -30452,10 +30452,10 @@
         <v/>
       </c>
       <c r="S302" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T302" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U302" t="str">
         <v/>
@@ -30541,10 +30541,10 @@
         <v>-</v>
       </c>
       <c r="S303" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T303" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U303" t="str">
         <v/>
@@ -30630,10 +30630,10 @@
         <v>041333</v>
       </c>
       <c r="S304" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T304" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U304" t="str">
         <v/>
@@ -30719,10 +30719,10 @@
         <v>041340</v>
       </c>
       <c r="S305" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T305" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U305" t="str">
         <v/>
@@ -30808,10 +30808,10 @@
         <v>041357</v>
       </c>
       <c r="S306" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T306" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U306" t="str">
         <v/>
@@ -30897,10 +30897,10 @@
         <v>-</v>
       </c>
       <c r="S307" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T307" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U307" t="str">
         <v/>
@@ -30986,10 +30986,10 @@
         <v>045119</v>
       </c>
       <c r="S308" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T308" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U308" t="str">
         <v/>
@@ -31075,10 +31075,10 @@
         <v>045126</v>
       </c>
       <c r="S309" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T309" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U309" t="str">
         <v/>
@@ -31164,10 +31164,10 @@
         <v>045133</v>
       </c>
       <c r="S310" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T310" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U310" t="str">
         <v/>
@@ -31253,10 +31253,10 @@
         <v>045140</v>
       </c>
       <c r="S311" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T311" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U311" t="str">
         <v/>
@@ -31342,10 +31342,10 @@
         <v>045157</v>
       </c>
       <c r="S312" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T312" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U312" t="str">
         <v/>
@@ -31431,10 +31431,10 @@
         <v>045164</v>
       </c>
       <c r="S313" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T313" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U313" t="str">
         <v/>
@@ -31520,10 +31520,10 @@
         <v>045171</v>
       </c>
       <c r="S314" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T314" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U314" t="str">
         <v/>
@@ -31609,10 +31609,10 @@
         <v>045188</v>
       </c>
       <c r="S315" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T315" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U315" t="str">
         <v/>
@@ -31698,10 +31698,10 @@
         <v>045195</v>
       </c>
       <c r="S316" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T316" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U316" t="str">
         <v/>
@@ -31787,10 +31787,10 @@
         <v>045201</v>
       </c>
       <c r="S317" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T317" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U317" t="str">
         <v/>
@@ -31876,10 +31876,10 @@
         <v>045218</v>
       </c>
       <c r="S318" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T318" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U318" t="str">
         <v/>
@@ -31965,10 +31965,10 @@
         <v>048066</v>
       </c>
       <c r="S319" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T319" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U319" t="str">
         <v/>
@@ -32054,10 +32054,10 @@
         <v>048073</v>
       </c>
       <c r="S320" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T320" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U320" t="str">
         <v/>
@@ -32143,10 +32143,10 @@
         <v>048080</v>
       </c>
       <c r="S321" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T321" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U321" t="str">
         <v/>
@@ -32232,10 +32232,10 @@
         <v>048097</v>
       </c>
       <c r="S322" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T322" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U322" t="str">
         <v/>
@@ -32321,10 +32321,10 @@
         <v>048103</v>
       </c>
       <c r="S323" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T323" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U323" t="str">
         <v/>
@@ -32410,10 +32410,10 @@
         <v>048110</v>
       </c>
       <c r="S324" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T324" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U324" t="str">
         <v/>
@@ -32499,10 +32499,10 @@
         <v>048127</v>
       </c>
       <c r="S325" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T325" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U325" t="str">
         <v/>
@@ -32588,10 +32588,10 @@
         <v>048134</v>
       </c>
       <c r="S326" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T326" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U326" t="str">
         <v/>
@@ -32677,10 +32677,10 @@
         <v>048141</v>
       </c>
       <c r="S327" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T327" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U327" t="str">
         <v/>
@@ -32766,10 +32766,10 @@
         <v>048158</v>
       </c>
       <c r="S328" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T328" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U328" t="str">
         <v/>
@@ -32855,10 +32855,10 @@
         <v>048165</v>
       </c>
       <c r="S329" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T329" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U329" t="str">
         <v/>
@@ -32944,10 +32944,10 @@
         <v>048172</v>
       </c>
       <c r="S330" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T330" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U330" t="str">
         <v/>
@@ -33033,10 +33033,10 @@
         <v/>
       </c>
       <c r="S331" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T331" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U331" t="str">
         <v/>
@@ -33122,10 +33122,10 @@
         <v/>
       </c>
       <c r="S332" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T332" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U332" t="str">
         <v/>
@@ -33211,10 +33211,10 @@
         <v/>
       </c>
       <c r="S333" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T333" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U333" t="str">
         <v/>
@@ -33300,10 +33300,10 @@
         <v/>
       </c>
       <c r="S334" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T334" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U334" t="str">
         <v/>
@@ -33389,10 +33389,10 @@
         <v/>
       </c>
       <c r="S335" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T335" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U335" t="str">
         <v/>
@@ -33478,10 +33478,10 @@
         <v/>
       </c>
       <c r="S336" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T336" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U336" t="str">
         <v/>
@@ -33567,10 +33567,10 @@
         <v/>
       </c>
       <c r="S337" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T337" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U337" t="str">
         <v/>
@@ -33656,10 +33656,10 @@
         <v>044495</v>
       </c>
       <c r="S338" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T338" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U338" t="str">
         <v/>
@@ -33745,10 +33745,10 @@
         <v>044501</v>
       </c>
       <c r="S339" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T339" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U339" t="str">
         <v/>
@@ -33834,10 +33834,10 @@
         <v>044518</v>
       </c>
       <c r="S340" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T340" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U340" t="str">
         <v/>
@@ -33923,10 +33923,10 @@
         <v>044525</v>
       </c>
       <c r="S341" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T341" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U341" t="str">
         <v/>
@@ -34012,10 +34012,10 @@
         <v>044532</v>
       </c>
       <c r="S342" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T342" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U342" t="str">
         <v/>
@@ -34101,10 +34101,10 @@
         <v>044549</v>
       </c>
       <c r="S343" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T343" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U343" t="str">
         <v/>
@@ -34190,10 +34190,10 @@
         <v>044556</v>
       </c>
       <c r="S344" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T344" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U344" t="str">
         <v/>
@@ -34279,10 +34279,10 @@
         <v>044563</v>
       </c>
       <c r="S345" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T345" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U345" t="str">
         <v/>
@@ -34368,10 +34368,10 @@
         <v>044570</v>
       </c>
       <c r="S346" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T346" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U346" t="str">
         <v/>
@@ -34457,10 +34457,10 @@
         <v>044587</v>
       </c>
       <c r="S347" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T347" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U347" t="str">
         <v/>
@@ -34546,10 +34546,10 @@
         <v>044594</v>
       </c>
       <c r="S348" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T348" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U348" t="str">
         <v/>
@@ -34635,10 +34635,10 @@
         <v>044600</v>
       </c>
       <c r="S349" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T349" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U349" t="str">
         <v/>
@@ -34724,10 +34724,10 @@
         <v>048233</v>
       </c>
       <c r="S350" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T350" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U350" t="str">
         <v/>
@@ -34813,10 +34813,10 @@
         <v>048240</v>
       </c>
       <c r="S351" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T351" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U351" t="str">
         <v/>
@@ -34902,10 +34902,10 @@
         <v>048257</v>
       </c>
       <c r="S352" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T352" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U352" t="str">
         <v/>
@@ -34991,10 +34991,10 @@
         <v>048264</v>
       </c>
       <c r="S353" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T353" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U353" t="str">
         <v/>
@@ -35080,10 +35080,10 @@
         <v>048271</v>
       </c>
       <c r="S354" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T354" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U354" t="str">
         <v/>
@@ -35169,10 +35169,10 @@
         <v>037732</v>
       </c>
       <c r="S355" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T355" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U355" t="str">
         <v/>
@@ -35258,10 +35258,10 @@
         <v>037749</v>
       </c>
       <c r="S356" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T356" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U356" t="str">
         <v/>
@@ -35347,10 +35347,10 @@
         <v>046413</v>
       </c>
       <c r="S357" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T357" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U357" t="str">
         <v/>
@@ -35436,10 +35436,10 @@
         <v>046420</v>
       </c>
       <c r="S358" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T358" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U358" t="str">
         <v/>
@@ -35525,10 +35525,10 @@
         <v>046437</v>
       </c>
       <c r="S359" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T359" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U359" t="str">
         <v/>
@@ -35614,10 +35614,10 @@
         <v>046444</v>
       </c>
       <c r="S360" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T360" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U360" t="str">
         <v/>
@@ -35703,10 +35703,10 @@
         <v>046451</v>
       </c>
       <c r="S361" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T361" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U361" t="str">
         <v/>
@@ -35792,10 +35792,10 @@
         <v>046468</v>
       </c>
       <c r="S362" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T362" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U362" t="str">
         <v/>
@@ -35881,10 +35881,10 @@
         <v>046475</v>
       </c>
       <c r="S363" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T363" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U363" t="str">
         <v/>
@@ -35970,10 +35970,10 @@
         <v>046482</v>
       </c>
       <c r="S364" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T364" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U364" t="str">
         <v/>
@@ -36059,10 +36059,10 @@
         <v>046499</v>
       </c>
       <c r="S365" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T365" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U365" t="str">
         <v/>
@@ -36148,10 +36148,10 @@
         <v>046505</v>
       </c>
       <c r="S366" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T366" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U366" t="str">
         <v/>
@@ -36237,10 +36237,10 @@
         <v>046512</v>
       </c>
       <c r="S367" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T367" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U367" t="str">
         <v/>
@@ -36326,10 +36326,10 @@
         <v>046529</v>
       </c>
       <c r="S368" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T368" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U368" t="str">
         <v/>
@@ -36415,10 +36415,10 @@
         <v>046536</v>
       </c>
       <c r="S369" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T369" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U369" t="str">
         <v/>
@@ -36504,10 +36504,10 @@
         <v>046543</v>
       </c>
       <c r="S370" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T370" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U370" t="str">
         <v/>
@@ -36593,10 +36593,10 @@
         <v>027757</v>
       </c>
       <c r="S371" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T371" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U371" t="str">
         <v/>
@@ -36682,10 +36682,10 @@
         <v>027764</v>
       </c>
       <c r="S372" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T372" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U372" t="str">
         <v/>
@@ -36771,10 +36771,10 @@
         <v>039163</v>
       </c>
       <c r="S373" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T373" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U373" t="str">
         <v/>
@@ -36860,10 +36860,10 @@
         <v>039187</v>
       </c>
       <c r="S374" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T374" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U374" t="str">
         <v/>
@@ -36949,10 +36949,10 @@
         <v>049445</v>
       </c>
       <c r="S375" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T375" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U375" t="str">
         <v/>
@@ -37038,10 +37038,10 @@
         <v>049452</v>
       </c>
       <c r="S376" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T376" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U376" t="str">
         <v/>
@@ -37127,10 +37127,10 @@
         <v>049469</v>
       </c>
       <c r="S377" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T377" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U377" t="str">
         <v/>
@@ -37216,10 +37216,10 @@
         <v>049476</v>
       </c>
       <c r="S378" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T378" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U378" t="str">
         <v/>
@@ -37305,10 +37305,10 @@
         <v>049483</v>
       </c>
       <c r="S379" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T379" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U379" t="str">
         <v/>
@@ -37394,10 +37394,10 @@
         <v>049490</v>
       </c>
       <c r="S380" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T380" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U380" t="str">
         <v/>
@@ -37483,10 +37483,10 @@
         <v>049506</v>
       </c>
       <c r="S381" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T381" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U381" t="str">
         <v/>
@@ -37572,10 +37572,10 @@
         <v>049513</v>
       </c>
       <c r="S382" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T382" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U382" t="str">
         <v/>
@@ -37661,10 +37661,10 @@
         <v>049520</v>
       </c>
       <c r="S383" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T383" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U383" t="str">
         <v/>
@@ -37750,10 +37750,10 @@
         <v>049537</v>
       </c>
       <c r="S384" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T384" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U384" t="str">
         <v/>
@@ -37839,10 +37839,10 @@
         <v>049544</v>
       </c>
       <c r="S385" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T385" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U385" t="str">
         <v/>
@@ -37928,10 +37928,10 @@
         <v/>
       </c>
       <c r="S386" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T386" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U386" t="str">
         <v/>
@@ -38017,10 +38017,10 @@
         <v/>
       </c>
       <c r="S387" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T387" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U387" t="str">
         <v/>
@@ -38106,10 +38106,10 @@
         <v/>
       </c>
       <c r="S388" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T388" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U388" t="str">
         <v/>
@@ -38195,10 +38195,10 @@
         <v/>
       </c>
       <c r="S389" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T389" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U389" t="str">
         <v/>
@@ -38284,10 +38284,10 @@
         <v/>
       </c>
       <c r="S390" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T390" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U390" t="str">
         <v/>
@@ -38373,10 +38373,10 @@
         <v/>
       </c>
       <c r="S391" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T391" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U391" t="str">
         <v/>
@@ -38462,10 +38462,10 @@
         <v/>
       </c>
       <c r="S392" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T392" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U392" t="str">
         <v/>
@@ -38551,10 +38551,10 @@
         <v/>
       </c>
       <c r="S393" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T393" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U393" t="str">
         <v/>
@@ -38640,10 +38640,10 @@
         <v/>
       </c>
       <c r="S394" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T394" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U394" t="str">
         <v/>
@@ -38729,10 +38729,10 @@
         <v/>
       </c>
       <c r="S395" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T395" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U395" t="str">
         <v/>
@@ -38818,10 +38818,10 @@
         <v/>
       </c>
       <c r="S396" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T396" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U396" t="str">
         <v/>
@@ -38907,10 +38907,10 @@
         <v/>
       </c>
       <c r="S397" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T397" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U397" t="str">
         <v/>
@@ -38996,10 +38996,10 @@
         <v/>
       </c>
       <c r="S398" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T398" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U398" t="str">
         <v/>
@@ -39085,10 +39085,10 @@
         <v/>
       </c>
       <c r="S399" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T399" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U399" t="str">
         <v/>
@@ -39174,10 +39174,10 @@
         <v/>
       </c>
       <c r="S400" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T400" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U400" t="str">
         <v/>
@@ -39263,10 +39263,10 @@
         <v/>
       </c>
       <c r="S401" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T401" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U401" t="str">
         <v/>
@@ -39352,10 +39352,10 @@
         <v/>
       </c>
       <c r="S402" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T402" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U402" t="str">
         <v/>
@@ -39441,10 +39441,10 @@
         <v/>
       </c>
       <c r="S403" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T403" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U403" t="str">
         <v/>
@@ -39530,10 +39530,10 @@
         <v/>
       </c>
       <c r="S404" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T404" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U404" t="str">
         <v/>
@@ -39619,10 +39619,10 @@
         <v/>
       </c>
       <c r="S405" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="T405" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="U405" t="str">
         <v/>

--- a/GearSage-client/pkgGear/data_raw/shimano_spinning_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_spinning_reels_import.xlsx
@@ -473,7 +473,7 @@
         <v>spinning</v>
       </c>
       <c r="I2" t="str">
-        <v>images/shimano_reels/STELLA SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA%20SW_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -520,7 +520,7 @@
         <v>spinning</v>
       </c>
       <c r="I3" t="str">
-        <v>images/shimano_reels/BB-X TECHNIUM FIRE BLOOD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20TECHNIUM%20FIRE%20BLOOD_main.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -567,7 +567,7 @@
         <v>spinning</v>
       </c>
       <c r="I4" t="str">
-        <v>images/shimano_reels/BB-X TECHNIUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20TECHNIUM%20FIRE%20BLOOD_main.jpg</v>
       </c>
       <c r="J4" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -614,7 +614,7 @@
         <v>spinning</v>
       </c>
       <c r="I5" t="str">
-        <v>images/shimano_reels/KISU SPECIAL 45_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/KISU%20SPECIAL%2045_main.jpg</v>
       </c>
       <c r="J5" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -661,7 +661,7 @@
         <v>spinning</v>
       </c>
       <c r="I6" t="str">
-        <v>images/shimano_reels/AERO TECHNIUM MGS XTD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20TECHNIUM%20MGS%20XTD_main.jpg</v>
       </c>
       <c r="J6" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -708,7 +708,7 @@
         <v>spinning</v>
       </c>
       <c r="I7" t="str">
-        <v>images/shimano_reels/AERO TECHNIUM MGS XSD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20TECHNIUM%20MGS%20XSD_main.jpg</v>
       </c>
       <c r="J7" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -755,7 +755,7 @@
         <v>spinning</v>
       </c>
       <c r="I8" t="str">
-        <v>images/shimano_reels/STELLA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA_main.jpg</v>
       </c>
       <c r="J8" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -802,7 +802,7 @@
         <v>spinning</v>
       </c>
       <c r="I9" t="str">
-        <v>images/shimano_reels/EXSENCE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE_main.jpg</v>
       </c>
       <c r="J9" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -849,7 +849,7 @@
         <v>spinning</v>
       </c>
       <c r="I10" t="str">
-        <v>images/shimano_reels/TWINPOWER SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER%20SW_main.jpg</v>
       </c>
       <c r="J10" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -896,7 +896,7 @@
         <v>spinning</v>
       </c>
       <c r="I11" t="str">
-        <v>images/shimano_reels/POWER AERO XTC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/POWER%20AERO%20XTC_main.jpg</v>
       </c>
       <c r="J11" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -943,7 +943,7 @@
         <v>spinning</v>
       </c>
       <c r="I12" t="str">
-        <v>images/shimano_reels/POWER AERO XSC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/POWER%20AERO%20XSC_main.jpg</v>
       </c>
       <c r="J12" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -990,7 +990,7 @@
         <v>spinning</v>
       </c>
       <c r="I13" t="str">
-        <v>images/shimano_reels/BB-X HYPER FORCE TYPE2_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20HYPER%20FORCE%20TYPE2_main.jpg</v>
       </c>
       <c r="J13" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1037,7 +1037,7 @@
         <v>spinning</v>
       </c>
       <c r="I14" t="str">
-        <v>images/shimano_reels/FLIEGEN_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/FLIEGEN_main.jpg</v>
       </c>
       <c r="J14" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1084,7 +1084,7 @@
         <v>spinning</v>
       </c>
       <c r="I15" t="str">
-        <v>images/shimano_reels/Vanquish CE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Vanquish%20CE_main.jpg</v>
       </c>
       <c r="J15" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1131,7 +1131,7 @@
         <v>spinning</v>
       </c>
       <c r="I16" t="str">
-        <v>images/shimano_reels/Vanquish_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Vanquish_main.jpg</v>
       </c>
       <c r="J16" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1178,7 +1178,7 @@
         <v>spinning</v>
       </c>
       <c r="I17" t="str">
-        <v>images/shimano_reels/SARAGOSA SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SARAGOSA%20SW_main.jpg</v>
       </c>
       <c r="J17" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1225,7 +1225,7 @@
         <v>spinning</v>
       </c>
       <c r="I18" t="str">
-        <v>images/shimano_reels/BB-X HYPER FORCE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20HYPER%20FORCE%201700_C2000_main.jpg</v>
       </c>
       <c r="J18" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1272,7 +1272,7 @@
         <v>spinning</v>
       </c>
       <c r="I19" t="str">
-        <v>images/shimano_reels/BB-X Remare_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20Remare_main.jpg</v>
       </c>
       <c r="J19" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1319,7 +1319,7 @@
         <v>spinning</v>
       </c>
       <c r="I20" t="str">
-        <v>images/shimano_reels/TWINPOWER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER_main.jpg</v>
       </c>
       <c r="J20" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1366,7 +1366,7 @@
         <v>spinning</v>
       </c>
       <c r="I21" t="str">
-        <v>images/shimano_reels/TWINPOWER XD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER%20XD_main.jpg</v>
       </c>
       <c r="J21" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1413,7 +1413,7 @@
         <v>spinning</v>
       </c>
       <c r="I22" t="str">
-        <v>images/shimano_reels/HYPER FORCE LB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/HYPER%20FORCE%20LB_main.jpg</v>
       </c>
       <c r="J22" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1460,7 +1460,7 @@
         <v>spinning</v>
       </c>
       <c r="I23" t="str">
-        <v>images/shimano_reels/POWER AERO TD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/POWER%20AERO%20TD_main.jpg</v>
       </c>
       <c r="J23" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1507,7 +1507,7 @@
         <v>spinning</v>
       </c>
       <c r="I24" t="str">
-        <v>images/shimano_reels/ULTEGRA XR BIG PIT XTD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA%20XR%20BIG%20PIT%20XTD_main.jpg</v>
       </c>
       <c r="J24" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1554,7 +1554,7 @@
         <v>spinning</v>
       </c>
       <c r="I25" t="str">
-        <v>images/shimano_reels/ULTEGRA XR BIG PIT XSD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA%20XR%20BIG%20PIT%20XSD_main.jpg</v>
       </c>
       <c r="J25" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1601,7 +1601,7 @@
         <v>spinning</v>
       </c>
       <c r="I26" t="str">
-        <v>images/shimano_reels/BB-X HYPER FORCE 1700_C2000_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20HYPER%20FORCE%201700_C2000_main.jpg</v>
       </c>
       <c r="J26" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1648,7 +1648,7 @@
         <v>spinning</v>
       </c>
       <c r="I27" t="str">
-        <v>images/shimano_reels/BB-X Rinkai SP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20Rinkai%20SP_main.jpg</v>
       </c>
       <c r="J27" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1695,7 +1695,7 @@
         <v>spinning</v>
       </c>
       <c r="I28" t="str">
-        <v>images/shimano_reels/EXSENCE XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20XR_main.jpg</v>
       </c>
       <c r="J28" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1742,7 +1742,7 @@
         <v>spinning</v>
       </c>
       <c r="I29" t="str">
-        <v>images/shimano_reels/STRADIC SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STRADIC%20SW_main.jpg</v>
       </c>
       <c r="J29" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1789,7 +1789,7 @@
         <v>spinning</v>
       </c>
       <c r="I30" t="str">
-        <v>images/shimano_reels/Sephia XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20XR_main.jpg</v>
       </c>
       <c r="J30" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1836,7 +1836,7 @@
         <v>spinning</v>
       </c>
       <c r="I31" t="str">
-        <v>images/shimano_reels/SUSTAIN_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SUSTAIN_main.jpg</v>
       </c>
       <c r="J31" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1883,7 +1883,7 @@
         <v>spinning</v>
       </c>
       <c r="I32" t="str">
-        <v>images/shimano_reels/Soare XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare%20XR_main.jpg</v>
       </c>
       <c r="J32" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1930,7 +1930,7 @@
         <v>spinning</v>
       </c>
       <c r="I33" t="str">
-        <v>images/shimano_reels/CARDIFF XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CARDIFF%20XR_main.jpg</v>
       </c>
       <c r="J33" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1977,7 +1977,7 @@
         <v>spinning</v>
       </c>
       <c r="I34" t="str">
-        <v>images/shimano_reels/BB-X DESPINA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20DESPINA_main.jpg</v>
       </c>
       <c r="J34" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2024,7 +2024,7 @@
         <v>spinning</v>
       </c>
       <c r="I35" t="str">
-        <v>images/shimano_reels/BULL‘S EYE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BULL%E2%80%98S%20EYE_main.jpg</v>
       </c>
       <c r="J35" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2071,7 +2071,7 @@
         <v>spinning</v>
       </c>
       <c r="I36" t="str">
-        <v>images/shimano_reels/COMPLEX XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/COMPLEX%20XR_main.jpg</v>
       </c>
       <c r="J36" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2118,7 +2118,7 @@
         <v>spinning</v>
       </c>
       <c r="I37" t="str">
-        <v>images/shimano_reels/BAITRUNNER CI4+ XTB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BAITRUNNER%20CI4%2B%20XTB_main.jpg</v>
       </c>
       <c r="J37" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2165,7 +2165,7 @@
         <v>spinning</v>
       </c>
       <c r="I38" t="str">
-        <v>images/shimano_reels/SURF LEADER_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SURF%20LEADER_main.png</v>
       </c>
       <c r="J38" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2212,7 +2212,7 @@
         <v>spinning</v>
       </c>
       <c r="I39" t="str">
-        <v>images/shimano_reels/Sephia SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20SS_main.jpg</v>
       </c>
       <c r="J39" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2259,7 +2259,7 @@
         <v>spinning</v>
       </c>
       <c r="I40" t="str">
-        <v>images/shimano_reels/VANFORD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/VANFORD_main.jpg</v>
       </c>
       <c r="J40" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2306,7 +2306,7 @@
         <v>spinning</v>
       </c>
       <c r="I41" t="str">
-        <v>images/shimano_reels/ULTEGRA XS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA%20XS_main.jpg</v>
       </c>
       <c r="J41" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2353,7 +2353,7 @@
         <v>spinning</v>
       </c>
       <c r="I42" t="str">
-        <v>images/shimano_reels/ULTEGRA XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA%20XT_main.jpg</v>
       </c>
       <c r="J42" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2400,7 +2400,7 @@
         <v>spinning</v>
       </c>
       <c r="I43" t="str">
-        <v>images/shimano_reels/BB-X LARISSA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20LARISSA_main.jpg</v>
       </c>
       <c r="J43" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2447,7 +2447,7 @@
         <v>spinning</v>
       </c>
       <c r="I44" t="str">
-        <v>images/shimano_reels/SPHEROS SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPHEROS%20SW_main.jpg</v>
       </c>
       <c r="J44" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2494,7 +2494,7 @@
         <v>spinning</v>
       </c>
       <c r="I45" t="str">
-        <v>images/shimano_reels/SPEEDMASTER XTD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPEEDMASTER%20XTD_main.jpg</v>
       </c>
       <c r="J45" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2541,7 +2541,7 @@
         <v>spinning</v>
       </c>
       <c r="I46" t="str">
-        <v>images/shimano_reels/STRADIC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STRADIC_main.jpg</v>
       </c>
       <c r="J46" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2588,7 +2588,7 @@
         <v>spinning</v>
       </c>
       <c r="I47" t="str">
-        <v>images/shimano_reels/SUPER AERO SpinJoy_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SUPER%20AERO%20SpinJoy_main.jpg</v>
       </c>
       <c r="J47" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2635,7 +2635,7 @@
         <v>spinning</v>
       </c>
       <c r="I48" t="str">
-        <v>images/shimano_reels/SPEEDMASTER XSD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPEEDMASTER%20XSD_main.jpg</v>
       </c>
       <c r="J48" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2682,7 +2682,7 @@
         <v>spinning</v>
       </c>
       <c r="I49" t="str">
-        <v>images/shimano_reels/Sephia BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20BB_main.jpg</v>
       </c>
       <c r="J49" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2729,7 +2729,7 @@
         <v>spinning</v>
       </c>
       <c r="I50" t="str">
-        <v>images/shimano_reels/EXSENCE BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20BB_main.jpg</v>
       </c>
       <c r="J50" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2776,7 +2776,7 @@
         <v>spinning</v>
       </c>
       <c r="I51" t="str">
-        <v>images/shimano_reels/AERO XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20XR_main.jpg</v>
       </c>
       <c r="J51" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2823,7 +2823,7 @@
         <v>spinning</v>
       </c>
       <c r="I52" t="str">
-        <v>images/shimano_reels/ULTEGRA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA_main.jpg</v>
       </c>
       <c r="J52" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2870,7 +2870,7 @@
         <v>spinning</v>
       </c>
       <c r="I53" t="str">
-        <v>images/shimano_reels/Soare BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare%20BB_main.jpg</v>
       </c>
       <c r="J53" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2917,7 +2917,7 @@
         <v>spinning</v>
       </c>
       <c r="I54" t="str">
-        <v>images/shimano_reels/AERLEX XTC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERLEX%20XTC_main.jpg</v>
       </c>
       <c r="J54" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2964,7 +2964,7 @@
         <v>spinning</v>
       </c>
       <c r="I55" t="str">
-        <v>images/shimano_reels/AERLEX XSC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERLEX%20XSC_main.jpg</v>
       </c>
       <c r="J55" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3011,7 +3011,7 @@
         <v>spinning</v>
       </c>
       <c r="I56" t="str">
-        <v>images/shimano_reels/AERO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO_main.jpg</v>
       </c>
       <c r="J56" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3058,7 +3058,7 @@
         <v>spinning</v>
       </c>
       <c r="I57" t="str">
-        <v>images/shimano_reels/MIRAVEL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/MIRAVEL_main.jpg</v>
       </c>
       <c r="J57" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3105,7 +3105,7 @@
         <v>spinning</v>
       </c>
       <c r="I58" t="str">
-        <v>images/shimano_reels/NASCI_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/NASCI_main.jpg</v>
       </c>
       <c r="J58" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3152,7 +3152,7 @@
         <v>spinning</v>
       </c>
       <c r="I59" t="str">
-        <v>images/shimano_reels/SOCORRO SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SOCORRO%20SW_main.jpg</v>
       </c>
       <c r="J59" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3199,7 +3199,7 @@
         <v>spinning</v>
       </c>
       <c r="I60" t="str">
-        <v>images/shimano_reels/AERO BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20BB_main.jpg</v>
       </c>
       <c r="J60" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3246,7 +3246,7 @@
         <v>spinning</v>
       </c>
       <c r="I61" t="str">
-        <v>images/shimano_reels/SAHARA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SAHARA_main.jpg</v>
       </c>
       <c r="J61" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3293,7 +3293,7 @@
         <v>spinning</v>
       </c>
       <c r="I62" t="str">
-        <v>images/shimano_reels/ACTIVECAST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ACTIVECAST_main.jpg</v>
       </c>
       <c r="J62" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3340,7 +3340,7 @@
         <v>spinning</v>
       </c>
       <c r="I63" t="str">
-        <v>images/shimano_reels/SEDONA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SEDONA_main.jpg</v>
       </c>
       <c r="J63" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3387,7 +3387,7 @@
         <v>spinning</v>
       </c>
       <c r="I64" t="str">
-        <v>images/shimano_reels/ALIVIO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALIVIO_main.jpg</v>
       </c>
       <c r="J64" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3434,7 +3434,7 @@
         <v>spinning</v>
       </c>
       <c r="I65" t="str">
-        <v>images/shimano_reels/NEXAVE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/NEXAVE_main.jpg</v>
       </c>
       <c r="J65" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3481,7 +3481,7 @@
         <v>spinning</v>
       </c>
       <c r="I66" t="str">
-        <v>images/shimano_reels/CATANA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CATANA_main.jpg</v>
       </c>
       <c r="J66" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3528,7 +3528,7 @@
         <v>spinning</v>
       </c>
       <c r="I67" t="str">
-        <v>images/shimano_reels/SIENNA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SIENNA_main.jpg</v>
       </c>
       <c r="J67" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3575,7 +3575,7 @@
         <v>spinning</v>
       </c>
       <c r="I68" t="str">
-        <v>images/shimano_reels/FX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/FX_main.jpg</v>
       </c>
       <c r="J68" t="str">
         <v>2026-04-10 00:51:20</v>

--- a/GearSage-client/pkgGear/data_raw/shimano_spinning_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_spinning_reels_import.xlsx
@@ -3354,7 +3354,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>STELLA SW 4000HG</t>
+          <t>4000HG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>STELLA SW 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>STELLA SW 5000HG</t>
+          <t>5000HG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>STELLA SW 5000XG</t>
+          <t>5000XG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>STELLA SW 6000PG</t>
+          <t>6000PG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>STELLA SW 6000HG</t>
+          <t>6000HG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>STELLA SW 6000XG</t>
+          <t>6000XG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>STELLA SW 8000PG</t>
+          <t>8000PG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>STELLA SW 8000HG</t>
+          <t>8000HG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>STELLA SW 8000XG</t>
+          <t>8000XG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STELLA SW 10000PG</t>
+          <t>10000PG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>STELLA SW 10000HG</t>
+          <t>10000HG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>STELLA SW 14000XG</t>
+          <t>14000XG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>STELLA SW 18000HG</t>
+          <t>18000HG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>STELLA SW 20000PG</t>
+          <t>20000PG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>STELLA SW 30000PG</t>
+          <t>30000PG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>STELLA SW 25000PG</t>
+          <t>25000PG</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>STELLA SW 4000HG</t>
+          <t>4000HG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>STELLA SW 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>STELLA SW 5000HG</t>
+          <t>5000HG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>STELLA SW 5000XG</t>
+          <t>5000XG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>STELLA SW 6000PG</t>
+          <t>6000PG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>STELLA SW 6000HG</t>
+          <t>6000HG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>STELLA SW 6000XG</t>
+          <t>6000XG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>STELLA SW 8000HG</t>
+          <t>8000HG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>STELLA SW 8000PG</t>
+          <t>8000PG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>STELLA SW 10000PG</t>
+          <t>10000PG</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>STELLA SW 14000PG</t>
+          <t>14000PG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>STELLA SW 14000XG</t>
+          <t>14000XG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>STELLA SW 18000HG</t>
+          <t>18000HG</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>STELLA SW 20000PG</t>
+          <t>20000PG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>STELLA SW 30000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>STELLA SW 10000HG</t>
+          <t>10000HG</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>STELLA 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>STELLA 1000SSPG</t>
+          <t>1000SSPG</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>STELLA C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>STELLA C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>STELLA C2500S</t>
+          <t>C2500S</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STELLA C2500SXG</t>
+          <t>C2500SXG</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>STELLA 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>STELLA 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>STELLA 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>STELLA 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>STELLA C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>STELLA C3000SDH</t>
+          <t>C3000SDH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>STELLA C3000SDHHG</t>
+          <t>C3000SDHHG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>STELLA C3000MHG</t>
+          <t>C3000MHG</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>STELLA C3000XG</t>
+          <t>C3000XG</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>STELLA 3000MHG</t>
+          <t>3000MHG</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>STELLA 4000M</t>
+          <t>4000M</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>STELLA 4000MHG</t>
+          <t>4000MHG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>STELLA 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>STELLA C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EXSENCE 2500XG</t>
+          <t>2500XG</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EXSENCE C3000MHG</t>
+          <t>C3000MHG</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EXSENCE 3000MHG</t>
+          <t>3000MHG</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EXSENCE 4000MXG</t>
+          <t>4000MXG</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 5000HG</t>
+          <t>5000HG</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 5000XG</t>
+          <t>5000XG</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 6000PG</t>
+          <t>6000PG</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 6000HG</t>
+          <t>6000HG</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 6000XG</t>
+          <t>6000XG</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 8000PG</t>
+          <t>8000PG</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 8000HG</t>
+          <t>8000HG</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 10000PG</t>
+          <t>10000PG</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 10000HG</t>
+          <t>10000HG</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 14000PG</t>
+          <t>14000PG</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TWINPOWER SW 14000XG</t>
+          <t>14000XG</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EXSENCE C3000MHG</t>
+          <t>C3000MHG</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EXSENCE C3000M</t>
+          <t>C3000M</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EXSENCE 3000MHG</t>
+          <t>3000MHG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EXSENCE 4000MXG</t>
+          <t>4000MXG</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vanquish CE 1000SSS</t>
+          <t>1000SSS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vanquish CE 1000SSSPG</t>
+          <t>1000SSSPG</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Vanquish CE C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vanquish CE C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Vanquish CE C2500S</t>
+          <t>C2500S</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Vanquish CE C2500SXG</t>
+          <t>C2500SXG</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Vanquish CE 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Vanquish CE 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Vanquish 1000SSSPG</t>
+          <t>1000SSSPG</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Vanquish C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Vanquish C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vanquish C2500S</t>
+          <t>C2500S</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Vanquish C2500SXG</t>
+          <t>C2500SXG</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Vanquish 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Vanquish 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Vanquish C3000SDH</t>
+          <t>C3000SDH</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Vanquish C3000SDHHG</t>
+          <t>C3000SDHHG</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Vanquish C3000MHG</t>
+          <t>C3000MHG</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Vanquish C3000XG</t>
+          <t>C3000XG</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Vanquish 3000MHG</t>
+          <t>3000MHG</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vanquish 4000MHG</t>
+          <t>4000MHG</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Vanquish 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vanquish C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SARAGOSA SW 5000XG</t>
+          <t>5000XG</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SARAGOSA SW 6000HG</t>
+          <t>6000HG</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SARAGOSA SW 8000HG</t>
+          <t>8000HG</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SARAGOSA SW 10000PG</t>
+          <t>10000PG</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SARAGOSA SW 14000XG</t>
+          <t>14000XG</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SARAGOSA SW 18000HG</t>
+          <t>18000HG</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SARAGOSA SW 20000PG</t>
+          <t>20000PG</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SARAGOSA SW 25000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TWINPOWER C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TWINPOWER C2500SXG</t>
+          <t>C2500SXG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TWINPOWER C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TWINPOWER 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TWINPOWER 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TWINPOWER 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TWINPOWER C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TWINPOWER C3000MHG</t>
+          <t>C3000MHG</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TWINPOWER C3000XG</t>
+          <t>C3000XG</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TWINPOWER 3000MHG</t>
+          <t>3000MHG</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TWINPOWER 4000M</t>
+          <t>4000M</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TWINPOWER 4000PG</t>
+          <t>4000PG</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TWINPOWER 4000MHG</t>
+          <t>4000MHG</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TWINPOWER 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16505,7 +16505,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TWINPOWER C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TWINPOWER XD C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TWINPOWER XD C3000XG</t>
+          <t>C3000XG</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TWINPOWER XD 4000PG</t>
+          <t>4000PG</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TWINPOWER XD 4000HG</t>
+          <t>4000HG</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TWINPOWER XD 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TWINPOWER XD C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EXSENCE XR C3000M</t>
+          <t>C3000M</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EXSENCE XR C3000MHG</t>
+          <t>C3000MHG</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>EXSENCE XR 3000MHG</t>
+          <t>3000MHG</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17615,7 +17615,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>EXSENCE XR 4000MXG</t>
+          <t>4000MXG</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>STRADIC SW 14000XG</t>
+          <t>14000XG</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sephia XR C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sephia XR C3000S</t>
+          <t>C3000S</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sephia XR C3000SDH</t>
+          <t>C3000SDH</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18130,7 +18130,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sephia XR C3000SHG</t>
+          <t>C3000SHG</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sephia XR C3000SDHHG</t>
+          <t>C3000SDHHG</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>STRADIC SW 4000HG</t>
+          <t>4000HG</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>STRADIC SW 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>STRADIC SW 5000XG</t>
+          <t>5000XG</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>STRADIC SW 6000PG</t>
+          <t>6000PG</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>STRADIC SW 6000HG</t>
+          <t>6000HG</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>STRADIC SW 6000XG</t>
+          <t>6000XG</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>STRADIC SW 8000PG</t>
+          <t>8000PG</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>STRADIC SW 8000HG</t>
+          <t>8000HG</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19190,7 +19190,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>STRADIC SW 10000HG</t>
+          <t>10000HG</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SUSTAIN 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19399,7 +19399,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SUSTAIN 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SUSTAIN C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SUSTAIN C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SUSTAIN 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SUSTAIN 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SUSTAIN C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20026,7 +20026,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sephia XR C3000S</t>
+          <t>C3000S</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Sephia XR C3000SDH</t>
+          <t>C3000SDH</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Sephia XR C3000SDHHG</t>
+          <t>C3000SDHHG</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Sephia XR C3000SHG</t>
+          <t>C3000SHG</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Soare XR 500SPG</t>
+          <t>500SPG</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Soare XR C2000SSPG</t>
+          <t>C2000SSPG</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Soare XR C2000SSHG</t>
+          <t>C2000SSHG</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20765,7 +20765,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Soare XR C2500SHG</t>
+          <t>C2500SHG</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CARDIFF XR C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -20989,7 +20989,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CARDIFF XR C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>COMPLEX XR C2500F4</t>
+          <t>C2500F4</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>COMPLEX XR C2500F4XG</t>
+          <t>C2500F4XG</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21325,7 +21325,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>COMPLEX XR 2500F6</t>
+          <t>2500F6</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21432,7 +21432,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>COMPLEX XR 2500F6HG</t>
+          <t>2500F6HG</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Soare XR C2000SSPG</t>
+          <t>C2000SSPG</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21651,7 +21651,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Soare XR C2000SSHG</t>
+          <t>C2000SSHG</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Soare XR C2500S</t>
+          <t>C2500S</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Soare XR 500SPG</t>
+          <t>500SPG</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sephia SS C3000S</t>
+          <t>C3000S</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Sephia SS C3000SDH</t>
+          <t>C3000SDH</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22186,7 +22186,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Sephia SS C3000SHG</t>
+          <t>C3000SHG</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Sephia SS C3000SDHHG</t>
+          <t>C3000SDHHG</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>VANFORD 500</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22507,7 +22507,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>VANFORD C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>VANFORD C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -22751,7 +22751,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>VANFORD C2000HG</t>
+          <t>C2000HG</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>VANFORD C2500S</t>
+          <t>C2500S</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>VANFORD C2500SXG</t>
+          <t>C2500SXG</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23117,7 +23117,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>VANFORD 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VANFORD 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>VANFORD 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23468,7 +23468,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>VANFORD 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>VANFORD C3000SDH</t>
+          <t>C3000SDH</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -23707,7 +23707,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>VANFORD C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>VANFORD C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -23951,7 +23951,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>VANFORD C3000XG</t>
+          <t>C3000XG</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24073,7 +24073,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>VANFORD 3000MHG</t>
+          <t>3000MHG</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24190,7 +24190,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>VANFORD 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>VANFORD 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -24424,7 +24424,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>VANFORD 4000MHG</t>
+          <t>4000MHG</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -24541,7 +24541,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>VANFORD C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>SPHEROS SW 5000XG</t>
+          <t>5000XG</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>SPHEROS SW 10000PG</t>
+          <t>10000PG</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -24867,7 +24867,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SPHEROS SW 14000XG</t>
+          <t>14000XG</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>SPHEROS SW 18000HG</t>
+          <t>18000HG</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>SPHEROS SW 20000PG</t>
+          <t>20000PG</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25173,7 +25173,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>SPHEROS SW 5000HG</t>
+          <t>5000HG</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -25275,7 +25275,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SPHEROS SW 6000PG</t>
+          <t>6000PG</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SPHEROS SW 6000HG</t>
+          <t>6000HG</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -25479,7 +25479,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SPHEROS SW 8000PG</t>
+          <t>8000PG</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -25581,7 +25581,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SPHEROS SW 8000HG</t>
+          <t>8000HG</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>STRADIC 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -25800,7 +25800,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>STRADIC 1000HG</t>
+          <t>1000HG</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>STRADIC C2000HG</t>
+          <t>C2000HG</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26039,7 +26039,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>STRADIC C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -26161,7 +26161,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>STRADIC C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>STRADIC C2500S</t>
+          <t>C2500S</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -26405,7 +26405,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>STRADIC C2500SXG</t>
+          <t>C2500SXG</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -26527,7 +26527,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>STRADIC 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -26644,7 +26644,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>STRADIC 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -26761,7 +26761,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>STRADIC 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -26878,7 +26878,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>STRADIC 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -26995,7 +26995,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>STRADIC C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>STRADIC C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -27239,7 +27239,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>STRADIC C3000XG</t>
+          <t>C3000XG</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -27361,7 +27361,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>STRADIC 3000MHG</t>
+          <t>3000MHG</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -27478,7 +27478,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>STRADIC 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>STRADIC 4000MHG</t>
+          <t>4000MHG</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>STRADIC 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -27829,7 +27829,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>STRADIC C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -27951,7 +27951,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Sephia BB C3000S</t>
+          <t>C3000S</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -28053,7 +28053,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Sephia BB C3000SHG</t>
+          <t>C3000SHG</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -28155,7 +28155,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Sephia BB C3000SDH</t>
+          <t>C3000SDH</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -28257,7 +28257,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Sephia BB C3000SDHHG</t>
+          <t>C3000SDHHG</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -28359,7 +28359,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>EXSENCE BB C3000MHG</t>
+          <t>C3000MHG</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>EXSENCE BB 3000MHG</t>
+          <t>3000MHG</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -28598,7 +28598,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>EXSENCE BB 4000MHG</t>
+          <t>4000MHG</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -28715,7 +28715,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>EXSENCE BB 4000MXG</t>
+          <t>4000MXG</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>AERO XR C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -28939,7 +28939,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>AERO XR 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -29041,7 +29041,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>AERO XR C5000</t>
+          <t>C5000</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -29148,7 +29148,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ULTEGRA 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -29265,7 +29265,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ULTEGRA C2000HG</t>
+          <t>C2000HG</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ULTEGRA C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -29509,7 +29509,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ULTEGRA C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -29631,7 +29631,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ULTEGRA C2500SHG</t>
+          <t>C2500SHG</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ULTEGRA 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -29870,7 +29870,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ULTEGRA 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -29987,7 +29987,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ULTEGRA 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -30104,7 +30104,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ULTEGRA C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -30226,7 +30226,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ULTEGRA C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -30348,7 +30348,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ULTEGRA C3000XG</t>
+          <t>C3000XG</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ULTEGRA 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -30587,7 +30587,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ULTEGRA 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ULTEGRA C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -30826,7 +30826,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Soare BB 500SPG</t>
+          <t>500SPG</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -30933,7 +30933,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Soare BB C2000SSPG</t>
+          <t>C2000SSPG</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -31045,7 +31045,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Soare BB C2000SSHG</t>
+          <t>C2000SSHG</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -31157,7 +31157,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>AERO C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -31264,7 +31264,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>AERO 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -31366,7 +31366,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>AERO C5000</t>
+          <t>C5000</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -31473,7 +31473,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>SPHEROS SW C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -31585,7 +31585,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>SPHEROS SW 3000XG</t>
+          <t>3000XG</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -31692,7 +31692,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>SPHEROS SW 4000HG</t>
+          <t>4000HG</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -31799,7 +31799,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>SPHEROS SW 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -31906,7 +31906,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>MIRAVEL 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -32023,7 +32023,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>MIRAVEL 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -32140,7 +32140,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>MIRAVEL C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -32262,7 +32262,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>MIRAVEL C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -32384,7 +32384,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>MIRAVEL 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -32501,7 +32501,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>MIRAVEL 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -32618,7 +32618,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>MIRAVEL 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -32735,7 +32735,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>MIRAVEL C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -32857,7 +32857,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>MIRAVEL C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32979,7 +32979,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>MIRAVEL 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -33096,7 +33096,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>MIRAVEL 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -33213,7 +33213,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>MIRAVEL C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -33335,7 +33335,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>NASCI 500</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -33452,7 +33452,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>NASCI 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>NASCI C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -33691,7 +33691,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>NASCI C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>NASCI 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33930,7 +33930,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>NASCI 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -34047,7 +34047,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>NASCI 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -34164,7 +34164,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>NASCI C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>NASCI C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -34408,7 +34408,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>NASCI 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -34525,7 +34525,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>NASCI 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -34642,7 +34642,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>NASCI C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -34764,7 +34764,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>SOCORRO SW 5000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -34861,7 +34861,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SOCORRO SW 6000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34958,7 +34958,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>SOCORRO SW 8000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -35055,7 +35055,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>SOCORRO SW 10000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -35152,7 +35152,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>AERO BB C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -35259,7 +35259,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>AERO BB 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -35361,7 +35361,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>AERO BB C5000</t>
+          <t>C5000</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -35468,7 +35468,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>SAHARA 500</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>SAHARA 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>SAHARA C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35824,7 +35824,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>SAHARA C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>SAHARA 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>SAHARA 2500SHG</t>
+          <t>2500SHG</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -36180,7 +36180,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>SAHARA C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -36302,7 +36302,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>SAHARA C3000DH</t>
+          <t>C3000DH</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -36424,7 +36424,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>SAHARA C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -36546,7 +36546,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>SAHARA 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -36663,7 +36663,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>SAHARA 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -36780,7 +36780,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>SAHARA C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -36902,7 +36902,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>SEDONA 6000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -37004,7 +37004,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>SEDONA 8000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -37106,7 +37106,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>SEDONA 500</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -37223,7 +37223,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>SEDONA 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -37340,7 +37340,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>SEDONA C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>SEDONA C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>SEDONA 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -37701,7 +37701,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>SEDONA 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -37818,7 +37818,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>SEDONA 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -37935,7 +37935,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SEDONA 2500S_PE1010</t>
+          <t>2500S_PE1010</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>SEDONA 2500SDH</t>
+          <t>2500SDH</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -38169,7 +38169,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>SEDONA C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -38291,7 +38291,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>SEDONA C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -38413,7 +38413,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>SEDONA 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -38530,7 +38530,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>SEDONA 4000XG</t>
+          <t>4000XG</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -38647,7 +38647,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>SEDONA C5000XG</t>
+          <t>C5000XG</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -38769,7 +38769,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ALIVIO 6000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -38876,7 +38876,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>ALIVIO 8000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>NEXAVE 6000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -39090,7 +39090,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>NEXAVE 8000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -39197,7 +39197,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>NEXAVE 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>NEXAVE C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -39426,7 +39426,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>NEXAVE C2000SHG</t>
+          <t>C2000SHG</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -39543,7 +39543,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>NEXAVE 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -39655,7 +39655,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>NEXAVE 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -39767,7 +39767,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>NEXAVE 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -39879,7 +39879,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>NEXAVE C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -39996,7 +39996,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>NEXAVE C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -40113,7 +40113,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>NEXAVE 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -40225,7 +40225,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>NEXAVE 4000HG</t>
+          <t>4000HG</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -40337,7 +40337,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>NEXAVE C5000HG</t>
+          <t>C5000HG</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -40454,7 +40454,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>NEXAVE 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -40571,7 +40571,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>NEXAVE C2000S</t>
+          <t>C2000S</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -40693,7 +40693,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>NEXAVE 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -40810,7 +40810,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>NEXAVE 2500S</t>
+          <t>2500S</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>NEXAVE 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -41044,7 +41044,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>NEXAVE C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -41166,7 +41166,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>NEXAVE C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -41288,7 +41288,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>NEXAVE 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -41405,7 +41405,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>NEXAVE 4000HG</t>
+          <t>4000HG</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>NEXAVE C5000HG</t>
+          <t>C5000HG</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -41644,7 +41644,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>CATANA 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -41746,7 +41746,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>CATANA 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -41848,7 +41848,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>CATANA 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -41950,7 +41950,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>CATANA C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -42057,7 +42057,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>CATANA C3000HG</t>
+          <t>C3000HG</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -42164,7 +42164,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>CATANA 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>CATANA 4000HG</t>
+          <t>4000HG</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -42368,7 +42368,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>SIENNA 500</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -42470,7 +42470,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>SIENNA 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -42572,7 +42572,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>SIENNA 2000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -42674,7 +42674,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>SIENNA 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -42776,7 +42776,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>SIENNA 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -42878,7 +42878,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>SIENNA C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -42985,7 +42985,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>SIENNA 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -43087,7 +43087,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>FX 1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -43189,7 +43189,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>FX 2000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>FX 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -43393,7 +43393,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>FX 2500HG</t>
+          <t>2500HG</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -43495,7 +43495,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>FX C3000</t>
+          <t>C3000</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -43602,7 +43602,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>FX 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
